--- a/Controlo_TVDE_Lisboa.xlsx
+++ b/Controlo_TVDE_Lisboa.xlsx
@@ -82,6 +82,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="N2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Valor REAL do que pagaste a carregar. Preenche na linha do turno em que carregaste. Se um carregamento der para vários turnos, mete tudo no turno em que pagaste — ao fim do mês o total fica certo à mesma. Deixa vazio nos turnos em que não carregaste.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Calculado a partir dos km e do valor por km definido na Config (manutenção e pneus).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="P2" authorId="0">
       <text>
         <r>
@@ -110,8 +134,30 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Valor por preencher. Enquanto estiver vazio conta como 0 € e o resultado mensal aparece melhor do que é na realidade.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="172">
   <si>
     <t xml:space="preserve">Controlo TVDE — Lisboa</t>
   </si>
@@ -125,7 +171,7 @@
     <t xml:space="preserve">1. Config</t>
   </si>
   <si>
-    <t xml:space="preserve">Começa aqui. Define a comissão da plataforma, o custo por km e os teus custos fixos mensais. Sem isto, os líquidos saem errados.</t>
+    <t xml:space="preserve">Começa aqui. Confirma a comissão da plataforma, o custo de manutenção e pneus por km, e os custos fixos mensais. Sem isto, os líquidos saem errados.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Registo Diário</t>
@@ -144,6 +190,27 @@
   </si>
   <si>
     <t xml:space="preserve">O que interessa é o €/hora LÍQUIDO, não a faturação. Um turno de 200 € com 11 horas e 250 km rende menos que um de 120 € com 5 horas e 80 km.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARREGAMENTOS (TESLA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coluna «Carregamento (€)»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A eletricidade NÃO é estimada. Sempre que carregares, mete o valor real que pagaste na linha do turno em que carregaste. Se um carregamento der para dois turnos, mete tudo no turno em que pagaste — ao fim do mês o total fica certo à mesma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo real por km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O «Resumo Mensal» calcula o teu € de carregamento por 100 km. Ao fim de um mês ficas a saber o custo real de energia do carro — melhor do que qualquer estimativa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carregar em casa vs rápido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carregar em casa fora do horário de ponta é muito mais barato do que carregamento rápido na rua. Se der, chega ao turno com o carro cheio de casa e usa a rede pública só como recurso.</t>
   </si>
   <si>
     <t xml:space="preserve">HORÁRIOS — PONTO DE PARTIDA</t>
@@ -254,6 +321,12 @@
     <t xml:space="preserve">Sintra, Cascais, Setúbal à hora de ponta: cuidado com o regresso vazio. 40 € com 50 min de volta a zero rende menos que três corridas urbanas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Autonomia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nos turnos de noite não deixes a bateria descer ao ponto de teres de parar 40 minutos a carregar na hora boa. Carrega antes de sair ou nas horas mortas do turno.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Multi-app</t>
   </si>
   <si>
@@ -278,7 +351,7 @@
     <t xml:space="preserve">Os horários e zonas acima são padrões gerais para orientar as primeiras semanas. Os teus próprios números, ao fim de 2-3 semanas de registo, valem mais do que qualquer regra geral — é para isso que serve esta folha.</t>
   </si>
   <si>
-    <t xml:space="preserve">REGISTO DIÁRIO  —  preenche só as colunas de cabeçalho AMARELO, uma linha por turno.  As colunas de cabeçalho CINZENTO são fórmulas: não escrevas nelas.  A linha 3 é um exemplo — apaga-a quando começares.</t>
+    <t xml:space="preserve">REGISTO DIÁRIO  —  preenche só as colunas de cabeçalho AZUL-ESCURO, uma linha por turno.  As colunas de cabeçalho CINZENTO são fórmulas: não escrevas nelas.  A linha 3 é um exemplo — apaga-a quando começares.</t>
   </si>
   <si>
     <t xml:space="preserve">Data</t>
@@ -320,10 +393,10 @@
     <t xml:space="preserve">Km</t>
   </si>
   <si>
-    <t xml:space="preserve">Energia (€)</t>
+    <t xml:space="preserve">Carregamento (€)</t>
   </si>
   <si>
-    <t xml:space="preserve">Desgaste (€)</t>
+    <t xml:space="preserve">Manut. e pneus (€)</t>
   </si>
   <si>
     <t xml:space="preserve">Portagens (€)</t>
@@ -353,7 +426,7 @@
     <t xml:space="preserve">Cais do Sodré / Bairro Alto</t>
   </si>
   <si>
-    <t xml:space="preserve">EXEMPLO — apaga esta linha. Muito movimento depois das 2h.</t>
+    <t xml:space="preserve">EXEMPLO — apaga esta linha. Carreguei a meio do turno.</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por bloco horário</t>
@@ -470,7 +543,7 @@
     <t xml:space="preserve">Resumo mensal — o que sobra mesmo</t>
   </si>
   <si>
-    <t xml:space="preserve">O «Líquido dos turnos» já desconta comissão, energia, desgaste, portagens e extras. Falta abater os custos fixos do mês (Config) para chegar ao RESULTADO — é esse o teu rendimento antes de impostos.</t>
+    <t xml:space="preserve">O «Líquido dos turnos» já desconta comissão, carregamentos, manutenção/pneus, portagens e extras. Falta abater os custos fixos do mês (prestação e seguro, na Config) para chegar ao RESULTADO — é esse o teu rendimento antes de impostos.</t>
   </si>
   <si>
     <t xml:space="preserve">Líquido dos turnos (€)</t>
@@ -488,7 +561,13 @@
     <t xml:space="preserve">Corridas</t>
   </si>
   <si>
-    <t xml:space="preserve">Os custos fixos só são debitados nos meses em que registaste turnos. O RESULTADO é antes de IRS e Segurança Social — reserva uma parte para isso. Se o «€/hora final» ficar abaixo do que ganharias noutro trabalho, os números estão a dizer-te alguma coisa.</t>
+    <t xml:space="preserve">Carregamentos (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energia por 100 km (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os custos fixos só são debitados nos meses em que registaste turnos. O RESULTADO é antes de IRS e Segurança Social — reserva uma parte. A coluna «Energia por 100 km» dá-te o custo real de eletricidade do carro a partir dos teus carregamentos.</t>
   </si>
   <si>
     <t xml:space="preserve">Config — pressupostos e custos</t>
@@ -506,7 +585,7 @@
     <t xml:space="preserve">Preenche as células amarelas. Tudo o resto na folha depende destes valores.</t>
   </si>
   <si>
-    <t xml:space="preserve">Custos variáveis</t>
+    <t xml:space="preserve">Custos variáveis (por km)</t>
   </si>
   <si>
     <t xml:space="preserve">Comissão da plataforma (%)</t>
@@ -515,16 +594,19 @@
     <t xml:space="preserve">Percentagem que a app retém sobre a faturação. Se a tua app já te mostra os ganhos JÁ líquidos de comissão, põe 0% aqui e regista esse valor na coluna Faturação.</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo de energia por km (€/km)</t>
+    <t xml:space="preserve">Manutenção e pneus por km (€/km)</t>
   </si>
   <si>
-    <t xml:space="preserve">Combustível ou eletricidade. Cálculo: preço do litro ÷ km por litro. Ex.: 1,75 €/L ÷ 16 km/L = 0,11 €/km. Elétrico em casa fica ~0,04 €/km.</t>
+    <t xml:space="preserve">Só manutenção e pneus. Num Tesla a fazer TVDE os pneus são o grosso: um jogo de ~800 € a durar ~35.000 km dá 0,023 €/km; o resto (alinhamentos, filtros, escovas, líquidos) fecha nos ~0,03 €/km. Ajusta quando tiveres faturas reais.</t>
   </si>
   <si>
-    <t xml:space="preserve">Desgaste e manutenção por km (€/km)</t>
+    <t xml:space="preserve">Eletricidade</t>
   </si>
   <si>
-    <t xml:space="preserve">Pneus, revisões, travões, óleo e depreciação do carro. 0,05-0,08 €/km é uma estimativa realista para um carro a fazer TVDE. Valor a ajustar quando tiveres histórico.</t>
+    <t xml:space="preserve">Não é estimada aqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metes o valor real de cada carregamento na coluna «Carregamento (€)» do Registo Diário. O Resumo Mensal calcula depois quanto te custa mesmo a energia por 100 km.</t>
   </si>
   <si>
     <t xml:space="preserve">Custos fixos mensais</t>
@@ -533,49 +615,34 @@
     <t xml:space="preserve">Custos que pagas mesmo que não trabalhes. Entram no separador «Resumo Mensal».</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguro TVDE</t>
+    <t xml:space="preserve">Prestação do carro</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguro com cobertura de atividade TVDE (mais caro que um seguro particular).</t>
+    <t xml:space="preserve">Prestação mensal do Tesla.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aluguer ou prestação da viatura</t>
+    <t xml:space="preserve">Seguro</t>
   </si>
   <si>
-    <t xml:space="preserve">Se o carro é teu e está pago, deixa a 0 — mas considera pôr aqui uma verba para o substituir.</t>
+    <t xml:space="preserve">A PREENCHER — seguro com cobertura de atividade TVDE. Mete o valor mensal assim que o tiveres.</t>
   </si>
   <si>
-    <t xml:space="preserve">Contabilidade</t>
+    <t xml:space="preserve">Outros custos fixos 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Contabilista certificado. Obrigatório se estiveres em contabilidade organizada.</t>
+    <t xml:space="preserve">Livre. Ex.: contabilidade, licenças TVDE mensalizadas, telemóvel, IUC e inspeção divididos por 12.</t>
   </si>
   <si>
-    <t xml:space="preserve">Licenças e certificados (mensalizado)</t>
+    <t xml:space="preserve">Outros custos fixos 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Certificado de motorista TVDE e dístico do veículo: divide o custo anual por 12.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telemóvel e dados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano de dados — precisas de rede estável o turno inteiro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspeção, IUC e outros anuais (mensalizado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soma os custos anuais do carro e divide por 12.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outros custos fixos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parque, lavagens por avença, o que mais tiveres.</t>
+    <t xml:space="preserve">Livre.</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL de custos fixos mensais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Só entram aqui os custos que listares acima. O que pagares e não estiver nesta lista não é abatido em lado nenhum — o resultado mensal sai por isso melhor do que a realidade.</t>
   </si>
   <si>
     <t xml:space="preserve">Primeiro mês de atividade</t>
@@ -622,7 +689,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="171" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,6 +860,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF008000"/>
@@ -894,7 +969,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1107,7 +1182,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1127,7 +1210,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1210,7 +1293,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1453,7 +1536,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C32"/>
+  <dimension ref="B1:C37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1477,7 +1560,7 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
@@ -1493,7 +1576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1501,7 +1584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
@@ -1515,7 +1598,7 @@
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
@@ -1523,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
@@ -1531,7 +1614,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
         <v>16</v>
       </c>
@@ -1539,29 +1622,29 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="5" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
@@ -1569,7 +1652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
         <v>25</v>
       </c>
@@ -1577,7 +1660,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
@@ -1585,37 +1668,37 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="5" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="5" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
         <v>36</v>
       </c>
@@ -1623,7 +1706,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1631,7 +1714,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
         <v>40</v>
       </c>
@@ -1639,21 +1722,21 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
         <v>45</v>
       </c>
@@ -1661,7 +1744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
         <v>47</v>
       </c>
@@ -1669,7 +1752,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
         <v>49</v>
       </c>
@@ -1677,20 +1760,58 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="7" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
         <v>54</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1843,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="10"/>
@@ -1733,7 +1856,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1759,70 +1882,70 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="V2" s="9" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1838,10 +1961,10 @@
         <v>46295</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F3" s="15" t="n">
         <v>0.895833333333333</v>
@@ -1869,13 +1992,12 @@
       <c r="M3" s="17" t="n">
         <v>122</v>
       </c>
-      <c r="N3" s="19" t="n">
+      <c r="N3" s="18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="O3" s="19" t="n">
         <f aca="false">IF($M3="","",$M3*Config!$B$6)</f>
-        <v>13.42</v>
-      </c>
-      <c r="O3" s="19" t="n">
-        <f aca="false">IF($M3="","",$M3*Config!$B$7)</f>
-        <v>7.32</v>
+        <v>3.66</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>3.2</v>
@@ -1885,22 +2007,22 @@
       </c>
       <c r="R3" s="20" t="n">
         <f aca="false">IF($J3="","",$J3-$K3+SUM($L3)-SUM($N3:$Q3))</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="S3" s="20" t="n">
         <f aca="false">IF(OR($R3="",$H3="",$H3=0),"",$R3/$H3)</f>
-        <v>16.44</v>
+        <v>17.2523076923077</v>
       </c>
       <c r="T3" s="19" t="n">
         <f aca="false">IF(OR($R3="",$M3="",$M3=0),"",$R3/$M3)</f>
-        <v>0.875901639344263</v>
+        <v>0.919180327868853</v>
       </c>
       <c r="U3" s="16" t="n">
         <f aca="false">IF(OR($H3="",$H3=0,$I3=""),"",$I3/$H3)</f>
         <v>2.15384615384615</v>
       </c>
       <c r="V3" s="14" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1929,12 +2051,9 @@
       </c>
       <c r="L4" s="28"/>
       <c r="M4" s="27"/>
-      <c r="N4" s="29" t="str">
+      <c r="N4" s="28"/>
+      <c r="O4" s="29" t="str">
         <f aca="false">IF($M4="","",$M4*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O4" s="29" t="str">
-        <f aca="false">IF($M4="","",$M4*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P4" s="28"/>
@@ -1983,12 +2102,9 @@
       </c>
       <c r="L5" s="28"/>
       <c r="M5" s="27"/>
-      <c r="N5" s="29" t="str">
+      <c r="N5" s="28"/>
+      <c r="O5" s="29" t="str">
         <f aca="false">IF($M5="","",$M5*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O5" s="29" t="str">
-        <f aca="false">IF($M5="","",$M5*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P5" s="28"/>
@@ -2037,12 +2153,9 @@
       </c>
       <c r="L6" s="28"/>
       <c r="M6" s="27"/>
-      <c r="N6" s="29" t="str">
+      <c r="N6" s="28"/>
+      <c r="O6" s="29" t="str">
         <f aca="false">IF($M6="","",$M6*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="29" t="str">
-        <f aca="false">IF($M6="","",$M6*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P6" s="28"/>
@@ -2091,12 +2204,9 @@
       </c>
       <c r="L7" s="28"/>
       <c r="M7" s="27"/>
-      <c r="N7" s="29" t="str">
+      <c r="N7" s="28"/>
+      <c r="O7" s="29" t="str">
         <f aca="false">IF($M7="","",$M7*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O7" s="29" t="str">
-        <f aca="false">IF($M7="","",$M7*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P7" s="28"/>
@@ -2145,12 +2255,9 @@
       </c>
       <c r="L8" s="28"/>
       <c r="M8" s="27"/>
-      <c r="N8" s="29" t="str">
+      <c r="N8" s="28"/>
+      <c r="O8" s="29" t="str">
         <f aca="false">IF($M8="","",$M8*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O8" s="29" t="str">
-        <f aca="false">IF($M8="","",$M8*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P8" s="28"/>
@@ -2199,12 +2306,9 @@
       </c>
       <c r="L9" s="28"/>
       <c r="M9" s="27"/>
-      <c r="N9" s="29" t="str">
+      <c r="N9" s="28"/>
+      <c r="O9" s="29" t="str">
         <f aca="false">IF($M9="","",$M9*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O9" s="29" t="str">
-        <f aca="false">IF($M9="","",$M9*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P9" s="28"/>
@@ -2253,12 +2357,9 @@
       </c>
       <c r="L10" s="28"/>
       <c r="M10" s="27"/>
-      <c r="N10" s="29" t="str">
+      <c r="N10" s="28"/>
+      <c r="O10" s="29" t="str">
         <f aca="false">IF($M10="","",$M10*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O10" s="29" t="str">
-        <f aca="false">IF($M10="","",$M10*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P10" s="28"/>
@@ -2307,12 +2408,9 @@
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="27"/>
-      <c r="N11" s="29" t="str">
+      <c r="N11" s="28"/>
+      <c r="O11" s="29" t="str">
         <f aca="false">IF($M11="","",$M11*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O11" s="29" t="str">
-        <f aca="false">IF($M11="","",$M11*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P11" s="28"/>
@@ -2361,12 +2459,9 @@
       </c>
       <c r="L12" s="28"/>
       <c r="M12" s="27"/>
-      <c r="N12" s="29" t="str">
+      <c r="N12" s="28"/>
+      <c r="O12" s="29" t="str">
         <f aca="false">IF($M12="","",$M12*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O12" s="29" t="str">
-        <f aca="false">IF($M12="","",$M12*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P12" s="28"/>
@@ -2415,12 +2510,9 @@
       </c>
       <c r="L13" s="28"/>
       <c r="M13" s="27"/>
-      <c r="N13" s="29" t="str">
+      <c r="N13" s="28"/>
+      <c r="O13" s="29" t="str">
         <f aca="false">IF($M13="","",$M13*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O13" s="29" t="str">
-        <f aca="false">IF($M13="","",$M13*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P13" s="28"/>
@@ -2469,12 +2561,9 @@
       </c>
       <c r="L14" s="28"/>
       <c r="M14" s="27"/>
-      <c r="N14" s="29" t="str">
+      <c r="N14" s="28"/>
+      <c r="O14" s="29" t="str">
         <f aca="false">IF($M14="","",$M14*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O14" s="29" t="str">
-        <f aca="false">IF($M14="","",$M14*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P14" s="28"/>
@@ -2523,12 +2612,9 @@
       </c>
       <c r="L15" s="28"/>
       <c r="M15" s="27"/>
-      <c r="N15" s="29" t="str">
+      <c r="N15" s="28"/>
+      <c r="O15" s="29" t="str">
         <f aca="false">IF($M15="","",$M15*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O15" s="29" t="str">
-        <f aca="false">IF($M15="","",$M15*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P15" s="28"/>
@@ -2577,12 +2663,9 @@
       </c>
       <c r="L16" s="28"/>
       <c r="M16" s="27"/>
-      <c r="N16" s="29" t="str">
+      <c r="N16" s="28"/>
+      <c r="O16" s="29" t="str">
         <f aca="false">IF($M16="","",$M16*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O16" s="29" t="str">
-        <f aca="false">IF($M16="","",$M16*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P16" s="28"/>
@@ -2631,12 +2714,9 @@
       </c>
       <c r="L17" s="28"/>
       <c r="M17" s="27"/>
-      <c r="N17" s="29" t="str">
+      <c r="N17" s="28"/>
+      <c r="O17" s="29" t="str">
         <f aca="false">IF($M17="","",$M17*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O17" s="29" t="str">
-        <f aca="false">IF($M17="","",$M17*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P17" s="28"/>
@@ -2685,12 +2765,9 @@
       </c>
       <c r="L18" s="28"/>
       <c r="M18" s="27"/>
-      <c r="N18" s="29" t="str">
+      <c r="N18" s="28"/>
+      <c r="O18" s="29" t="str">
         <f aca="false">IF($M18="","",$M18*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O18" s="29" t="str">
-        <f aca="false">IF($M18="","",$M18*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P18" s="28"/>
@@ -2739,12 +2816,9 @@
       </c>
       <c r="L19" s="28"/>
       <c r="M19" s="27"/>
-      <c r="N19" s="29" t="str">
+      <c r="N19" s="28"/>
+      <c r="O19" s="29" t="str">
         <f aca="false">IF($M19="","",$M19*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O19" s="29" t="str">
-        <f aca="false">IF($M19="","",$M19*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P19" s="28"/>
@@ -2793,12 +2867,9 @@
       </c>
       <c r="L20" s="28"/>
       <c r="M20" s="27"/>
-      <c r="N20" s="29" t="str">
+      <c r="N20" s="28"/>
+      <c r="O20" s="29" t="str">
         <f aca="false">IF($M20="","",$M20*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O20" s="29" t="str">
-        <f aca="false">IF($M20="","",$M20*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P20" s="28"/>
@@ -2847,12 +2918,9 @@
       </c>
       <c r="L21" s="28"/>
       <c r="M21" s="27"/>
-      <c r="N21" s="29" t="str">
+      <c r="N21" s="28"/>
+      <c r="O21" s="29" t="str">
         <f aca="false">IF($M21="","",$M21*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O21" s="29" t="str">
-        <f aca="false">IF($M21="","",$M21*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P21" s="28"/>
@@ -2901,12 +2969,9 @@
       </c>
       <c r="L22" s="28"/>
       <c r="M22" s="27"/>
-      <c r="N22" s="29" t="str">
+      <c r="N22" s="28"/>
+      <c r="O22" s="29" t="str">
         <f aca="false">IF($M22="","",$M22*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O22" s="29" t="str">
-        <f aca="false">IF($M22="","",$M22*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P22" s="28"/>
@@ -2955,12 +3020,9 @@
       </c>
       <c r="L23" s="28"/>
       <c r="M23" s="27"/>
-      <c r="N23" s="29" t="str">
+      <c r="N23" s="28"/>
+      <c r="O23" s="29" t="str">
         <f aca="false">IF($M23="","",$M23*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O23" s="29" t="str">
-        <f aca="false">IF($M23="","",$M23*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P23" s="28"/>
@@ -3009,12 +3071,9 @@
       </c>
       <c r="L24" s="28"/>
       <c r="M24" s="27"/>
-      <c r="N24" s="29" t="str">
+      <c r="N24" s="28"/>
+      <c r="O24" s="29" t="str">
         <f aca="false">IF($M24="","",$M24*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O24" s="29" t="str">
-        <f aca="false">IF($M24="","",$M24*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P24" s="28"/>
@@ -3063,12 +3122,9 @@
       </c>
       <c r="L25" s="28"/>
       <c r="M25" s="27"/>
-      <c r="N25" s="29" t="str">
+      <c r="N25" s="28"/>
+      <c r="O25" s="29" t="str">
         <f aca="false">IF($M25="","",$M25*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O25" s="29" t="str">
-        <f aca="false">IF($M25="","",$M25*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P25" s="28"/>
@@ -3117,12 +3173,9 @@
       </c>
       <c r="L26" s="28"/>
       <c r="M26" s="27"/>
-      <c r="N26" s="29" t="str">
+      <c r="N26" s="28"/>
+      <c r="O26" s="29" t="str">
         <f aca="false">IF($M26="","",$M26*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O26" s="29" t="str">
-        <f aca="false">IF($M26="","",$M26*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P26" s="28"/>
@@ -3171,12 +3224,9 @@
       </c>
       <c r="L27" s="28"/>
       <c r="M27" s="27"/>
-      <c r="N27" s="29" t="str">
+      <c r="N27" s="28"/>
+      <c r="O27" s="29" t="str">
         <f aca="false">IF($M27="","",$M27*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O27" s="29" t="str">
-        <f aca="false">IF($M27="","",$M27*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P27" s="28"/>
@@ -3225,12 +3275,9 @@
       </c>
       <c r="L28" s="28"/>
       <c r="M28" s="27"/>
-      <c r="N28" s="29" t="str">
+      <c r="N28" s="28"/>
+      <c r="O28" s="29" t="str">
         <f aca="false">IF($M28="","",$M28*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O28" s="29" t="str">
-        <f aca="false">IF($M28="","",$M28*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P28" s="28"/>
@@ -3279,12 +3326,9 @@
       </c>
       <c r="L29" s="28"/>
       <c r="M29" s="27"/>
-      <c r="N29" s="29" t="str">
+      <c r="N29" s="28"/>
+      <c r="O29" s="29" t="str">
         <f aca="false">IF($M29="","",$M29*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O29" s="29" t="str">
-        <f aca="false">IF($M29="","",$M29*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P29" s="28"/>
@@ -3333,12 +3377,9 @@
       </c>
       <c r="L30" s="28"/>
       <c r="M30" s="27"/>
-      <c r="N30" s="29" t="str">
+      <c r="N30" s="28"/>
+      <c r="O30" s="29" t="str">
         <f aca="false">IF($M30="","",$M30*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O30" s="29" t="str">
-        <f aca="false">IF($M30="","",$M30*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P30" s="28"/>
@@ -3387,12 +3428,9 @@
       </c>
       <c r="L31" s="28"/>
       <c r="M31" s="27"/>
-      <c r="N31" s="29" t="str">
+      <c r="N31" s="28"/>
+      <c r="O31" s="29" t="str">
         <f aca="false">IF($M31="","",$M31*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O31" s="29" t="str">
-        <f aca="false">IF($M31="","",$M31*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P31" s="28"/>
@@ -3441,12 +3479,9 @@
       </c>
       <c r="L32" s="28"/>
       <c r="M32" s="27"/>
-      <c r="N32" s="29" t="str">
+      <c r="N32" s="28"/>
+      <c r="O32" s="29" t="str">
         <f aca="false">IF($M32="","",$M32*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O32" s="29" t="str">
-        <f aca="false">IF($M32="","",$M32*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P32" s="28"/>
@@ -3495,12 +3530,9 @@
       </c>
       <c r="L33" s="28"/>
       <c r="M33" s="27"/>
-      <c r="N33" s="29" t="str">
+      <c r="N33" s="28"/>
+      <c r="O33" s="29" t="str">
         <f aca="false">IF($M33="","",$M33*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O33" s="29" t="str">
-        <f aca="false">IF($M33="","",$M33*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P33" s="28"/>
@@ -3549,12 +3581,9 @@
       </c>
       <c r="L34" s="28"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="29" t="str">
+      <c r="N34" s="28"/>
+      <c r="O34" s="29" t="str">
         <f aca="false">IF($M34="","",$M34*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O34" s="29" t="str">
-        <f aca="false">IF($M34="","",$M34*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P34" s="28"/>
@@ -3603,12 +3632,9 @@
       </c>
       <c r="L35" s="28"/>
       <c r="M35" s="27"/>
-      <c r="N35" s="29" t="str">
+      <c r="N35" s="28"/>
+      <c r="O35" s="29" t="str">
         <f aca="false">IF($M35="","",$M35*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O35" s="29" t="str">
-        <f aca="false">IF($M35="","",$M35*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P35" s="28"/>
@@ -3657,12 +3683,9 @@
       </c>
       <c r="L36" s="28"/>
       <c r="M36" s="27"/>
-      <c r="N36" s="29" t="str">
+      <c r="N36" s="28"/>
+      <c r="O36" s="29" t="str">
         <f aca="false">IF($M36="","",$M36*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O36" s="29" t="str">
-        <f aca="false">IF($M36="","",$M36*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P36" s="28"/>
@@ -3711,12 +3734,9 @@
       </c>
       <c r="L37" s="28"/>
       <c r="M37" s="27"/>
-      <c r="N37" s="29" t="str">
+      <c r="N37" s="28"/>
+      <c r="O37" s="29" t="str">
         <f aca="false">IF($M37="","",$M37*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O37" s="29" t="str">
-        <f aca="false">IF($M37="","",$M37*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P37" s="28"/>
@@ -3765,12 +3785,9 @@
       </c>
       <c r="L38" s="28"/>
       <c r="M38" s="27"/>
-      <c r="N38" s="29" t="str">
+      <c r="N38" s="28"/>
+      <c r="O38" s="29" t="str">
         <f aca="false">IF($M38="","",$M38*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O38" s="29" t="str">
-        <f aca="false">IF($M38="","",$M38*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P38" s="28"/>
@@ -3819,12 +3836,9 @@
       </c>
       <c r="L39" s="28"/>
       <c r="M39" s="27"/>
-      <c r="N39" s="29" t="str">
+      <c r="N39" s="28"/>
+      <c r="O39" s="29" t="str">
         <f aca="false">IF($M39="","",$M39*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O39" s="29" t="str">
-        <f aca="false">IF($M39="","",$M39*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P39" s="28"/>
@@ -3873,12 +3887,9 @@
       </c>
       <c r="L40" s="28"/>
       <c r="M40" s="27"/>
-      <c r="N40" s="29" t="str">
+      <c r="N40" s="28"/>
+      <c r="O40" s="29" t="str">
         <f aca="false">IF($M40="","",$M40*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O40" s="29" t="str">
-        <f aca="false">IF($M40="","",$M40*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P40" s="28"/>
@@ -3927,12 +3938,9 @@
       </c>
       <c r="L41" s="28"/>
       <c r="M41" s="27"/>
-      <c r="N41" s="29" t="str">
+      <c r="N41" s="28"/>
+      <c r="O41" s="29" t="str">
         <f aca="false">IF($M41="","",$M41*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O41" s="29" t="str">
-        <f aca="false">IF($M41="","",$M41*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P41" s="28"/>
@@ -3981,12 +3989,9 @@
       </c>
       <c r="L42" s="28"/>
       <c r="M42" s="27"/>
-      <c r="N42" s="29" t="str">
+      <c r="N42" s="28"/>
+      <c r="O42" s="29" t="str">
         <f aca="false">IF($M42="","",$M42*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O42" s="29" t="str">
-        <f aca="false">IF($M42="","",$M42*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P42" s="28"/>
@@ -4035,12 +4040,9 @@
       </c>
       <c r="L43" s="28"/>
       <c r="M43" s="27"/>
-      <c r="N43" s="29" t="str">
+      <c r="N43" s="28"/>
+      <c r="O43" s="29" t="str">
         <f aca="false">IF($M43="","",$M43*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O43" s="29" t="str">
-        <f aca="false">IF($M43="","",$M43*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P43" s="28"/>
@@ -4089,12 +4091,9 @@
       </c>
       <c r="L44" s="28"/>
       <c r="M44" s="27"/>
-      <c r="N44" s="29" t="str">
+      <c r="N44" s="28"/>
+      <c r="O44" s="29" t="str">
         <f aca="false">IF($M44="","",$M44*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O44" s="29" t="str">
-        <f aca="false">IF($M44="","",$M44*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P44" s="28"/>
@@ -4143,12 +4142,9 @@
       </c>
       <c r="L45" s="28"/>
       <c r="M45" s="27"/>
-      <c r="N45" s="29" t="str">
+      <c r="N45" s="28"/>
+      <c r="O45" s="29" t="str">
         <f aca="false">IF($M45="","",$M45*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O45" s="29" t="str">
-        <f aca="false">IF($M45="","",$M45*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P45" s="28"/>
@@ -4197,12 +4193,9 @@
       </c>
       <c r="L46" s="28"/>
       <c r="M46" s="27"/>
-      <c r="N46" s="29" t="str">
+      <c r="N46" s="28"/>
+      <c r="O46" s="29" t="str">
         <f aca="false">IF($M46="","",$M46*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O46" s="29" t="str">
-        <f aca="false">IF($M46="","",$M46*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P46" s="28"/>
@@ -4251,12 +4244,9 @@
       </c>
       <c r="L47" s="28"/>
       <c r="M47" s="27"/>
-      <c r="N47" s="29" t="str">
+      <c r="N47" s="28"/>
+      <c r="O47" s="29" t="str">
         <f aca="false">IF($M47="","",$M47*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O47" s="29" t="str">
-        <f aca="false">IF($M47="","",$M47*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P47" s="28"/>
@@ -4305,12 +4295,9 @@
       </c>
       <c r="L48" s="28"/>
       <c r="M48" s="27"/>
-      <c r="N48" s="29" t="str">
+      <c r="N48" s="28"/>
+      <c r="O48" s="29" t="str">
         <f aca="false">IF($M48="","",$M48*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O48" s="29" t="str">
-        <f aca="false">IF($M48="","",$M48*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P48" s="28"/>
@@ -4359,12 +4346,9 @@
       </c>
       <c r="L49" s="28"/>
       <c r="M49" s="27"/>
-      <c r="N49" s="29" t="str">
+      <c r="N49" s="28"/>
+      <c r="O49" s="29" t="str">
         <f aca="false">IF($M49="","",$M49*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O49" s="29" t="str">
-        <f aca="false">IF($M49="","",$M49*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P49" s="28"/>
@@ -4413,12 +4397,9 @@
       </c>
       <c r="L50" s="28"/>
       <c r="M50" s="27"/>
-      <c r="N50" s="29" t="str">
+      <c r="N50" s="28"/>
+      <c r="O50" s="29" t="str">
         <f aca="false">IF($M50="","",$M50*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O50" s="29" t="str">
-        <f aca="false">IF($M50="","",$M50*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P50" s="28"/>
@@ -4467,12 +4448,9 @@
       </c>
       <c r="L51" s="28"/>
       <c r="M51" s="27"/>
-      <c r="N51" s="29" t="str">
+      <c r="N51" s="28"/>
+      <c r="O51" s="29" t="str">
         <f aca="false">IF($M51="","",$M51*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O51" s="29" t="str">
-        <f aca="false">IF($M51="","",$M51*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P51" s="28"/>
@@ -4521,12 +4499,9 @@
       </c>
       <c r="L52" s="28"/>
       <c r="M52" s="27"/>
-      <c r="N52" s="29" t="str">
+      <c r="N52" s="28"/>
+      <c r="O52" s="29" t="str">
         <f aca="false">IF($M52="","",$M52*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O52" s="29" t="str">
-        <f aca="false">IF($M52="","",$M52*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P52" s="28"/>
@@ -4575,12 +4550,9 @@
       </c>
       <c r="L53" s="28"/>
       <c r="M53" s="27"/>
-      <c r="N53" s="29" t="str">
+      <c r="N53" s="28"/>
+      <c r="O53" s="29" t="str">
         <f aca="false">IF($M53="","",$M53*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O53" s="29" t="str">
-        <f aca="false">IF($M53="","",$M53*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P53" s="28"/>
@@ -4629,12 +4601,9 @@
       </c>
       <c r="L54" s="28"/>
       <c r="M54" s="27"/>
-      <c r="N54" s="29" t="str">
+      <c r="N54" s="28"/>
+      <c r="O54" s="29" t="str">
         <f aca="false">IF($M54="","",$M54*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O54" s="29" t="str">
-        <f aca="false">IF($M54="","",$M54*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P54" s="28"/>
@@ -4683,12 +4652,9 @@
       </c>
       <c r="L55" s="28"/>
       <c r="M55" s="27"/>
-      <c r="N55" s="29" t="str">
+      <c r="N55" s="28"/>
+      <c r="O55" s="29" t="str">
         <f aca="false">IF($M55="","",$M55*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O55" s="29" t="str">
-        <f aca="false">IF($M55="","",$M55*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P55" s="28"/>
@@ -4737,12 +4703,9 @@
       </c>
       <c r="L56" s="28"/>
       <c r="M56" s="27"/>
-      <c r="N56" s="29" t="str">
+      <c r="N56" s="28"/>
+      <c r="O56" s="29" t="str">
         <f aca="false">IF($M56="","",$M56*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O56" s="29" t="str">
-        <f aca="false">IF($M56="","",$M56*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P56" s="28"/>
@@ -4791,12 +4754,9 @@
       </c>
       <c r="L57" s="28"/>
       <c r="M57" s="27"/>
-      <c r="N57" s="29" t="str">
+      <c r="N57" s="28"/>
+      <c r="O57" s="29" t="str">
         <f aca="false">IF($M57="","",$M57*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O57" s="29" t="str">
-        <f aca="false">IF($M57="","",$M57*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P57" s="28"/>
@@ -4845,12 +4805,9 @@
       </c>
       <c r="L58" s="28"/>
       <c r="M58" s="27"/>
-      <c r="N58" s="29" t="str">
+      <c r="N58" s="28"/>
+      <c r="O58" s="29" t="str">
         <f aca="false">IF($M58="","",$M58*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O58" s="29" t="str">
-        <f aca="false">IF($M58="","",$M58*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P58" s="28"/>
@@ -4899,12 +4856,9 @@
       </c>
       <c r="L59" s="28"/>
       <c r="M59" s="27"/>
-      <c r="N59" s="29" t="str">
+      <c r="N59" s="28"/>
+      <c r="O59" s="29" t="str">
         <f aca="false">IF($M59="","",$M59*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O59" s="29" t="str">
-        <f aca="false">IF($M59="","",$M59*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P59" s="28"/>
@@ -4953,12 +4907,9 @@
       </c>
       <c r="L60" s="28"/>
       <c r="M60" s="27"/>
-      <c r="N60" s="29" t="str">
+      <c r="N60" s="28"/>
+      <c r="O60" s="29" t="str">
         <f aca="false">IF($M60="","",$M60*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O60" s="29" t="str">
-        <f aca="false">IF($M60="","",$M60*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P60" s="28"/>
@@ -5007,12 +4958,9 @@
       </c>
       <c r="L61" s="28"/>
       <c r="M61" s="27"/>
-      <c r="N61" s="29" t="str">
+      <c r="N61" s="28"/>
+      <c r="O61" s="29" t="str">
         <f aca="false">IF($M61="","",$M61*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O61" s="29" t="str">
-        <f aca="false">IF($M61="","",$M61*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P61" s="28"/>
@@ -5061,12 +5009,9 @@
       </c>
       <c r="L62" s="28"/>
       <c r="M62" s="27"/>
-      <c r="N62" s="29" t="str">
+      <c r="N62" s="28"/>
+      <c r="O62" s="29" t="str">
         <f aca="false">IF($M62="","",$M62*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O62" s="29" t="str">
-        <f aca="false">IF($M62="","",$M62*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P62" s="28"/>
@@ -5115,12 +5060,9 @@
       </c>
       <c r="L63" s="28"/>
       <c r="M63" s="27"/>
-      <c r="N63" s="29" t="str">
+      <c r="N63" s="28"/>
+      <c r="O63" s="29" t="str">
         <f aca="false">IF($M63="","",$M63*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O63" s="29" t="str">
-        <f aca="false">IF($M63="","",$M63*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P63" s="28"/>
@@ -5169,12 +5111,9 @@
       </c>
       <c r="L64" s="28"/>
       <c r="M64" s="27"/>
-      <c r="N64" s="29" t="str">
+      <c r="N64" s="28"/>
+      <c r="O64" s="29" t="str">
         <f aca="false">IF($M64="","",$M64*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O64" s="29" t="str">
-        <f aca="false">IF($M64="","",$M64*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P64" s="28"/>
@@ -5223,12 +5162,9 @@
       </c>
       <c r="L65" s="28"/>
       <c r="M65" s="27"/>
-      <c r="N65" s="29" t="str">
+      <c r="N65" s="28"/>
+      <c r="O65" s="29" t="str">
         <f aca="false">IF($M65="","",$M65*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O65" s="29" t="str">
-        <f aca="false">IF($M65="","",$M65*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P65" s="28"/>
@@ -5277,12 +5213,9 @@
       </c>
       <c r="L66" s="28"/>
       <c r="M66" s="27"/>
-      <c r="N66" s="29" t="str">
+      <c r="N66" s="28"/>
+      <c r="O66" s="29" t="str">
         <f aca="false">IF($M66="","",$M66*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O66" s="29" t="str">
-        <f aca="false">IF($M66="","",$M66*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P66" s="28"/>
@@ -5331,12 +5264,9 @@
       </c>
       <c r="L67" s="28"/>
       <c r="M67" s="27"/>
-      <c r="N67" s="29" t="str">
+      <c r="N67" s="28"/>
+      <c r="O67" s="29" t="str">
         <f aca="false">IF($M67="","",$M67*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O67" s="29" t="str">
-        <f aca="false">IF($M67="","",$M67*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P67" s="28"/>
@@ -5385,12 +5315,9 @@
       </c>
       <c r="L68" s="28"/>
       <c r="M68" s="27"/>
-      <c r="N68" s="29" t="str">
+      <c r="N68" s="28"/>
+      <c r="O68" s="29" t="str">
         <f aca="false">IF($M68="","",$M68*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O68" s="29" t="str">
-        <f aca="false">IF($M68="","",$M68*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P68" s="28"/>
@@ -5439,12 +5366,9 @@
       </c>
       <c r="L69" s="28"/>
       <c r="M69" s="27"/>
-      <c r="N69" s="29" t="str">
+      <c r="N69" s="28"/>
+      <c r="O69" s="29" t="str">
         <f aca="false">IF($M69="","",$M69*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O69" s="29" t="str">
-        <f aca="false">IF($M69="","",$M69*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P69" s="28"/>
@@ -5493,12 +5417,9 @@
       </c>
       <c r="L70" s="28"/>
       <c r="M70" s="27"/>
-      <c r="N70" s="29" t="str">
+      <c r="N70" s="28"/>
+      <c r="O70" s="29" t="str">
         <f aca="false">IF($M70="","",$M70*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O70" s="29" t="str">
-        <f aca="false">IF($M70="","",$M70*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P70" s="28"/>
@@ -5547,12 +5468,9 @@
       </c>
       <c r="L71" s="28"/>
       <c r="M71" s="27"/>
-      <c r="N71" s="29" t="str">
+      <c r="N71" s="28"/>
+      <c r="O71" s="29" t="str">
         <f aca="false">IF($M71="","",$M71*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O71" s="29" t="str">
-        <f aca="false">IF($M71="","",$M71*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P71" s="28"/>
@@ -5601,12 +5519,9 @@
       </c>
       <c r="L72" s="28"/>
       <c r="M72" s="27"/>
-      <c r="N72" s="29" t="str">
+      <c r="N72" s="28"/>
+      <c r="O72" s="29" t="str">
         <f aca="false">IF($M72="","",$M72*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O72" s="29" t="str">
-        <f aca="false">IF($M72="","",$M72*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P72" s="28"/>
@@ -5655,12 +5570,9 @@
       </c>
       <c r="L73" s="28"/>
       <c r="M73" s="27"/>
-      <c r="N73" s="29" t="str">
+      <c r="N73" s="28"/>
+      <c r="O73" s="29" t="str">
         <f aca="false">IF($M73="","",$M73*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O73" s="29" t="str">
-        <f aca="false">IF($M73="","",$M73*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P73" s="28"/>
@@ -5709,12 +5621,9 @@
       </c>
       <c r="L74" s="28"/>
       <c r="M74" s="27"/>
-      <c r="N74" s="29" t="str">
+      <c r="N74" s="28"/>
+      <c r="O74" s="29" t="str">
         <f aca="false">IF($M74="","",$M74*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O74" s="29" t="str">
-        <f aca="false">IF($M74="","",$M74*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P74" s="28"/>
@@ -5763,12 +5672,9 @@
       </c>
       <c r="L75" s="28"/>
       <c r="M75" s="27"/>
-      <c r="N75" s="29" t="str">
+      <c r="N75" s="28"/>
+      <c r="O75" s="29" t="str">
         <f aca="false">IF($M75="","",$M75*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O75" s="29" t="str">
-        <f aca="false">IF($M75="","",$M75*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P75" s="28"/>
@@ -5817,12 +5723,9 @@
       </c>
       <c r="L76" s="28"/>
       <c r="M76" s="27"/>
-      <c r="N76" s="29" t="str">
+      <c r="N76" s="28"/>
+      <c r="O76" s="29" t="str">
         <f aca="false">IF($M76="","",$M76*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O76" s="29" t="str">
-        <f aca="false">IF($M76="","",$M76*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P76" s="28"/>
@@ -5871,12 +5774,9 @@
       </c>
       <c r="L77" s="28"/>
       <c r="M77" s="27"/>
-      <c r="N77" s="29" t="str">
+      <c r="N77" s="28"/>
+      <c r="O77" s="29" t="str">
         <f aca="false">IF($M77="","",$M77*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O77" s="29" t="str">
-        <f aca="false">IF($M77="","",$M77*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P77" s="28"/>
@@ -5925,12 +5825,9 @@
       </c>
       <c r="L78" s="28"/>
       <c r="M78" s="27"/>
-      <c r="N78" s="29" t="str">
+      <c r="N78" s="28"/>
+      <c r="O78" s="29" t="str">
         <f aca="false">IF($M78="","",$M78*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O78" s="29" t="str">
-        <f aca="false">IF($M78="","",$M78*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P78" s="28"/>
@@ -5979,12 +5876,9 @@
       </c>
       <c r="L79" s="28"/>
       <c r="M79" s="27"/>
-      <c r="N79" s="29" t="str">
+      <c r="N79" s="28"/>
+      <c r="O79" s="29" t="str">
         <f aca="false">IF($M79="","",$M79*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O79" s="29" t="str">
-        <f aca="false">IF($M79="","",$M79*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P79" s="28"/>
@@ -6033,12 +5927,9 @@
       </c>
       <c r="L80" s="28"/>
       <c r="M80" s="27"/>
-      <c r="N80" s="29" t="str">
+      <c r="N80" s="28"/>
+      <c r="O80" s="29" t="str">
         <f aca="false">IF($M80="","",$M80*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O80" s="29" t="str">
-        <f aca="false">IF($M80="","",$M80*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P80" s="28"/>
@@ -6087,12 +5978,9 @@
       </c>
       <c r="L81" s="28"/>
       <c r="M81" s="27"/>
-      <c r="N81" s="29" t="str">
+      <c r="N81" s="28"/>
+      <c r="O81" s="29" t="str">
         <f aca="false">IF($M81="","",$M81*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O81" s="29" t="str">
-        <f aca="false">IF($M81="","",$M81*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P81" s="28"/>
@@ -6141,12 +6029,9 @@
       </c>
       <c r="L82" s="28"/>
       <c r="M82" s="27"/>
-      <c r="N82" s="29" t="str">
+      <c r="N82" s="28"/>
+      <c r="O82" s="29" t="str">
         <f aca="false">IF($M82="","",$M82*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O82" s="29" t="str">
-        <f aca="false">IF($M82="","",$M82*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P82" s="28"/>
@@ -6195,12 +6080,9 @@
       </c>
       <c r="L83" s="28"/>
       <c r="M83" s="27"/>
-      <c r="N83" s="29" t="str">
+      <c r="N83" s="28"/>
+      <c r="O83" s="29" t="str">
         <f aca="false">IF($M83="","",$M83*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O83" s="29" t="str">
-        <f aca="false">IF($M83="","",$M83*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P83" s="28"/>
@@ -6249,12 +6131,9 @@
       </c>
       <c r="L84" s="28"/>
       <c r="M84" s="27"/>
-      <c r="N84" s="29" t="str">
+      <c r="N84" s="28"/>
+      <c r="O84" s="29" t="str">
         <f aca="false">IF($M84="","",$M84*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O84" s="29" t="str">
-        <f aca="false">IF($M84="","",$M84*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P84" s="28"/>
@@ -6303,12 +6182,9 @@
       </c>
       <c r="L85" s="28"/>
       <c r="M85" s="27"/>
-      <c r="N85" s="29" t="str">
+      <c r="N85" s="28"/>
+      <c r="O85" s="29" t="str">
         <f aca="false">IF($M85="","",$M85*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O85" s="29" t="str">
-        <f aca="false">IF($M85="","",$M85*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P85" s="28"/>
@@ -6357,12 +6233,9 @@
       </c>
       <c r="L86" s="28"/>
       <c r="M86" s="27"/>
-      <c r="N86" s="29" t="str">
+      <c r="N86" s="28"/>
+      <c r="O86" s="29" t="str">
         <f aca="false">IF($M86="","",$M86*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O86" s="29" t="str">
-        <f aca="false">IF($M86="","",$M86*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P86" s="28"/>
@@ -6411,12 +6284,9 @@
       </c>
       <c r="L87" s="28"/>
       <c r="M87" s="27"/>
-      <c r="N87" s="29" t="str">
+      <c r="N87" s="28"/>
+      <c r="O87" s="29" t="str">
         <f aca="false">IF($M87="","",$M87*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O87" s="29" t="str">
-        <f aca="false">IF($M87="","",$M87*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P87" s="28"/>
@@ -6465,12 +6335,9 @@
       </c>
       <c r="L88" s="28"/>
       <c r="M88" s="27"/>
-      <c r="N88" s="29" t="str">
+      <c r="N88" s="28"/>
+      <c r="O88" s="29" t="str">
         <f aca="false">IF($M88="","",$M88*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O88" s="29" t="str">
-        <f aca="false">IF($M88="","",$M88*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P88" s="28"/>
@@ -6519,12 +6386,9 @@
       </c>
       <c r="L89" s="28"/>
       <c r="M89" s="27"/>
-      <c r="N89" s="29" t="str">
+      <c r="N89" s="28"/>
+      <c r="O89" s="29" t="str">
         <f aca="false">IF($M89="","",$M89*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O89" s="29" t="str">
-        <f aca="false">IF($M89="","",$M89*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P89" s="28"/>
@@ -6573,12 +6437,9 @@
       </c>
       <c r="L90" s="28"/>
       <c r="M90" s="27"/>
-      <c r="N90" s="29" t="str">
+      <c r="N90" s="28"/>
+      <c r="O90" s="29" t="str">
         <f aca="false">IF($M90="","",$M90*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O90" s="29" t="str">
-        <f aca="false">IF($M90="","",$M90*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P90" s="28"/>
@@ -6627,12 +6488,9 @@
       </c>
       <c r="L91" s="28"/>
       <c r="M91" s="27"/>
-      <c r="N91" s="29" t="str">
+      <c r="N91" s="28"/>
+      <c r="O91" s="29" t="str">
         <f aca="false">IF($M91="","",$M91*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O91" s="29" t="str">
-        <f aca="false">IF($M91="","",$M91*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P91" s="28"/>
@@ -6681,12 +6539,9 @@
       </c>
       <c r="L92" s="28"/>
       <c r="M92" s="27"/>
-      <c r="N92" s="29" t="str">
+      <c r="N92" s="28"/>
+      <c r="O92" s="29" t="str">
         <f aca="false">IF($M92="","",$M92*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O92" s="29" t="str">
-        <f aca="false">IF($M92="","",$M92*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P92" s="28"/>
@@ -6735,12 +6590,9 @@
       </c>
       <c r="L93" s="28"/>
       <c r="M93" s="27"/>
-      <c r="N93" s="29" t="str">
+      <c r="N93" s="28"/>
+      <c r="O93" s="29" t="str">
         <f aca="false">IF($M93="","",$M93*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O93" s="29" t="str">
-        <f aca="false">IF($M93="","",$M93*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P93" s="28"/>
@@ -6789,12 +6641,9 @@
       </c>
       <c r="L94" s="28"/>
       <c r="M94" s="27"/>
-      <c r="N94" s="29" t="str">
+      <c r="N94" s="28"/>
+      <c r="O94" s="29" t="str">
         <f aca="false">IF($M94="","",$M94*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O94" s="29" t="str">
-        <f aca="false">IF($M94="","",$M94*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P94" s="28"/>
@@ -6843,12 +6692,9 @@
       </c>
       <c r="L95" s="28"/>
       <c r="M95" s="27"/>
-      <c r="N95" s="29" t="str">
+      <c r="N95" s="28"/>
+      <c r="O95" s="29" t="str">
         <f aca="false">IF($M95="","",$M95*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O95" s="29" t="str">
-        <f aca="false">IF($M95="","",$M95*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P95" s="28"/>
@@ -6897,12 +6743,9 @@
       </c>
       <c r="L96" s="28"/>
       <c r="M96" s="27"/>
-      <c r="N96" s="29" t="str">
+      <c r="N96" s="28"/>
+      <c r="O96" s="29" t="str">
         <f aca="false">IF($M96="","",$M96*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O96" s="29" t="str">
-        <f aca="false">IF($M96="","",$M96*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P96" s="28"/>
@@ -6951,12 +6794,9 @@
       </c>
       <c r="L97" s="28"/>
       <c r="M97" s="27"/>
-      <c r="N97" s="29" t="str">
+      <c r="N97" s="28"/>
+      <c r="O97" s="29" t="str">
         <f aca="false">IF($M97="","",$M97*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O97" s="29" t="str">
-        <f aca="false">IF($M97="","",$M97*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P97" s="28"/>
@@ -7005,12 +6845,9 @@
       </c>
       <c r="L98" s="28"/>
       <c r="M98" s="27"/>
-      <c r="N98" s="29" t="str">
+      <c r="N98" s="28"/>
+      <c r="O98" s="29" t="str">
         <f aca="false">IF($M98="","",$M98*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O98" s="29" t="str">
-        <f aca="false">IF($M98="","",$M98*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P98" s="28"/>
@@ -7059,12 +6896,9 @@
       </c>
       <c r="L99" s="28"/>
       <c r="M99" s="27"/>
-      <c r="N99" s="29" t="str">
+      <c r="N99" s="28"/>
+      <c r="O99" s="29" t="str">
         <f aca="false">IF($M99="","",$M99*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O99" s="29" t="str">
-        <f aca="false">IF($M99="","",$M99*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P99" s="28"/>
@@ -7113,12 +6947,9 @@
       </c>
       <c r="L100" s="28"/>
       <c r="M100" s="27"/>
-      <c r="N100" s="29" t="str">
+      <c r="N100" s="28"/>
+      <c r="O100" s="29" t="str">
         <f aca="false">IF($M100="","",$M100*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O100" s="29" t="str">
-        <f aca="false">IF($M100="","",$M100*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P100" s="28"/>
@@ -7167,12 +6998,9 @@
       </c>
       <c r="L101" s="28"/>
       <c r="M101" s="27"/>
-      <c r="N101" s="29" t="str">
+      <c r="N101" s="28"/>
+      <c r="O101" s="29" t="str">
         <f aca="false">IF($M101="","",$M101*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O101" s="29" t="str">
-        <f aca="false">IF($M101="","",$M101*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P101" s="28"/>
@@ -7221,12 +7049,9 @@
       </c>
       <c r="L102" s="28"/>
       <c r="M102" s="27"/>
-      <c r="N102" s="29" t="str">
+      <c r="N102" s="28"/>
+      <c r="O102" s="29" t="str">
         <f aca="false">IF($M102="","",$M102*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O102" s="29" t="str">
-        <f aca="false">IF($M102="","",$M102*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P102" s="28"/>
@@ -7275,12 +7100,9 @@
       </c>
       <c r="L103" s="28"/>
       <c r="M103" s="27"/>
-      <c r="N103" s="29" t="str">
+      <c r="N103" s="28"/>
+      <c r="O103" s="29" t="str">
         <f aca="false">IF($M103="","",$M103*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O103" s="29" t="str">
-        <f aca="false">IF($M103="","",$M103*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P103" s="28"/>
@@ -7329,12 +7151,9 @@
       </c>
       <c r="L104" s="28"/>
       <c r="M104" s="27"/>
-      <c r="N104" s="29" t="str">
+      <c r="N104" s="28"/>
+      <c r="O104" s="29" t="str">
         <f aca="false">IF($M104="","",$M104*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O104" s="29" t="str">
-        <f aca="false">IF($M104="","",$M104*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P104" s="28"/>
@@ -7383,12 +7202,9 @@
       </c>
       <c r="L105" s="28"/>
       <c r="M105" s="27"/>
-      <c r="N105" s="29" t="str">
+      <c r="N105" s="28"/>
+      <c r="O105" s="29" t="str">
         <f aca="false">IF($M105="","",$M105*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O105" s="29" t="str">
-        <f aca="false">IF($M105="","",$M105*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P105" s="28"/>
@@ -7437,12 +7253,9 @@
       </c>
       <c r="L106" s="28"/>
       <c r="M106" s="27"/>
-      <c r="N106" s="29" t="str">
+      <c r="N106" s="28"/>
+      <c r="O106" s="29" t="str">
         <f aca="false">IF($M106="","",$M106*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O106" s="29" t="str">
-        <f aca="false">IF($M106="","",$M106*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P106" s="28"/>
@@ -7491,12 +7304,9 @@
       </c>
       <c r="L107" s="28"/>
       <c r="M107" s="27"/>
-      <c r="N107" s="29" t="str">
+      <c r="N107" s="28"/>
+      <c r="O107" s="29" t="str">
         <f aca="false">IF($M107="","",$M107*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O107" s="29" t="str">
-        <f aca="false">IF($M107="","",$M107*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P107" s="28"/>
@@ -7545,12 +7355,9 @@
       </c>
       <c r="L108" s="28"/>
       <c r="M108" s="27"/>
-      <c r="N108" s="29" t="str">
+      <c r="N108" s="28"/>
+      <c r="O108" s="29" t="str">
         <f aca="false">IF($M108="","",$M108*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O108" s="29" t="str">
-        <f aca="false">IF($M108="","",$M108*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P108" s="28"/>
@@ -7599,12 +7406,9 @@
       </c>
       <c r="L109" s="28"/>
       <c r="M109" s="27"/>
-      <c r="N109" s="29" t="str">
+      <c r="N109" s="28"/>
+      <c r="O109" s="29" t="str">
         <f aca="false">IF($M109="","",$M109*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O109" s="29" t="str">
-        <f aca="false">IF($M109="","",$M109*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P109" s="28"/>
@@ -7653,12 +7457,9 @@
       </c>
       <c r="L110" s="28"/>
       <c r="M110" s="27"/>
-      <c r="N110" s="29" t="str">
+      <c r="N110" s="28"/>
+      <c r="O110" s="29" t="str">
         <f aca="false">IF($M110="","",$M110*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O110" s="29" t="str">
-        <f aca="false">IF($M110="","",$M110*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P110" s="28"/>
@@ -7707,12 +7508,9 @@
       </c>
       <c r="L111" s="28"/>
       <c r="M111" s="27"/>
-      <c r="N111" s="29" t="str">
+      <c r="N111" s="28"/>
+      <c r="O111" s="29" t="str">
         <f aca="false">IF($M111="","",$M111*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O111" s="29" t="str">
-        <f aca="false">IF($M111="","",$M111*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P111" s="28"/>
@@ -7761,12 +7559,9 @@
       </c>
       <c r="L112" s="28"/>
       <c r="M112" s="27"/>
-      <c r="N112" s="29" t="str">
+      <c r="N112" s="28"/>
+      <c r="O112" s="29" t="str">
         <f aca="false">IF($M112="","",$M112*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O112" s="29" t="str">
-        <f aca="false">IF($M112="","",$M112*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P112" s="28"/>
@@ -7815,12 +7610,9 @@
       </c>
       <c r="L113" s="28"/>
       <c r="M113" s="27"/>
-      <c r="N113" s="29" t="str">
+      <c r="N113" s="28"/>
+      <c r="O113" s="29" t="str">
         <f aca="false">IF($M113="","",$M113*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O113" s="29" t="str">
-        <f aca="false">IF($M113="","",$M113*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P113" s="28"/>
@@ -7869,12 +7661,9 @@
       </c>
       <c r="L114" s="28"/>
       <c r="M114" s="27"/>
-      <c r="N114" s="29" t="str">
+      <c r="N114" s="28"/>
+      <c r="O114" s="29" t="str">
         <f aca="false">IF($M114="","",$M114*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O114" s="29" t="str">
-        <f aca="false">IF($M114="","",$M114*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P114" s="28"/>
@@ -7923,12 +7712,9 @@
       </c>
       <c r="L115" s="28"/>
       <c r="M115" s="27"/>
-      <c r="N115" s="29" t="str">
+      <c r="N115" s="28"/>
+      <c r="O115" s="29" t="str">
         <f aca="false">IF($M115="","",$M115*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O115" s="29" t="str">
-        <f aca="false">IF($M115="","",$M115*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P115" s="28"/>
@@ -7977,12 +7763,9 @@
       </c>
       <c r="L116" s="28"/>
       <c r="M116" s="27"/>
-      <c r="N116" s="29" t="str">
+      <c r="N116" s="28"/>
+      <c r="O116" s="29" t="str">
         <f aca="false">IF($M116="","",$M116*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O116" s="29" t="str">
-        <f aca="false">IF($M116="","",$M116*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P116" s="28"/>
@@ -8031,12 +7814,9 @@
       </c>
       <c r="L117" s="28"/>
       <c r="M117" s="27"/>
-      <c r="N117" s="29" t="str">
+      <c r="N117" s="28"/>
+      <c r="O117" s="29" t="str">
         <f aca="false">IF($M117="","",$M117*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O117" s="29" t="str">
-        <f aca="false">IF($M117="","",$M117*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P117" s="28"/>
@@ -8085,12 +7865,9 @@
       </c>
       <c r="L118" s="28"/>
       <c r="M118" s="27"/>
-      <c r="N118" s="29" t="str">
+      <c r="N118" s="28"/>
+      <c r="O118" s="29" t="str">
         <f aca="false">IF($M118="","",$M118*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O118" s="29" t="str">
-        <f aca="false">IF($M118="","",$M118*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P118" s="28"/>
@@ -8139,12 +7916,9 @@
       </c>
       <c r="L119" s="28"/>
       <c r="M119" s="27"/>
-      <c r="N119" s="29" t="str">
+      <c r="N119" s="28"/>
+      <c r="O119" s="29" t="str">
         <f aca="false">IF($M119="","",$M119*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O119" s="29" t="str">
-        <f aca="false">IF($M119="","",$M119*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P119" s="28"/>
@@ -8193,12 +7967,9 @@
       </c>
       <c r="L120" s="28"/>
       <c r="M120" s="27"/>
-      <c r="N120" s="29" t="str">
+      <c r="N120" s="28"/>
+      <c r="O120" s="29" t="str">
         <f aca="false">IF($M120="","",$M120*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O120" s="29" t="str">
-        <f aca="false">IF($M120="","",$M120*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P120" s="28"/>
@@ -8247,12 +8018,9 @@
       </c>
       <c r="L121" s="28"/>
       <c r="M121" s="27"/>
-      <c r="N121" s="29" t="str">
+      <c r="N121" s="28"/>
+      <c r="O121" s="29" t="str">
         <f aca="false">IF($M121="","",$M121*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O121" s="29" t="str">
-        <f aca="false">IF($M121="","",$M121*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P121" s="28"/>
@@ -8301,12 +8069,9 @@
       </c>
       <c r="L122" s="28"/>
       <c r="M122" s="27"/>
-      <c r="N122" s="29" t="str">
+      <c r="N122" s="28"/>
+      <c r="O122" s="29" t="str">
         <f aca="false">IF($M122="","",$M122*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O122" s="29" t="str">
-        <f aca="false">IF($M122="","",$M122*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P122" s="28"/>
@@ -8355,12 +8120,9 @@
       </c>
       <c r="L123" s="28"/>
       <c r="M123" s="27"/>
-      <c r="N123" s="29" t="str">
+      <c r="N123" s="28"/>
+      <c r="O123" s="29" t="str">
         <f aca="false">IF($M123="","",$M123*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O123" s="29" t="str">
-        <f aca="false">IF($M123="","",$M123*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P123" s="28"/>
@@ -8409,12 +8171,9 @@
       </c>
       <c r="L124" s="28"/>
       <c r="M124" s="27"/>
-      <c r="N124" s="29" t="str">
+      <c r="N124" s="28"/>
+      <c r="O124" s="29" t="str">
         <f aca="false">IF($M124="","",$M124*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O124" s="29" t="str">
-        <f aca="false">IF($M124="","",$M124*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P124" s="28"/>
@@ -8463,12 +8222,9 @@
       </c>
       <c r="L125" s="28"/>
       <c r="M125" s="27"/>
-      <c r="N125" s="29" t="str">
+      <c r="N125" s="28"/>
+      <c r="O125" s="29" t="str">
         <f aca="false">IF($M125="","",$M125*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O125" s="29" t="str">
-        <f aca="false">IF($M125="","",$M125*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P125" s="28"/>
@@ -8517,12 +8273,9 @@
       </c>
       <c r="L126" s="28"/>
       <c r="M126" s="27"/>
-      <c r="N126" s="29" t="str">
+      <c r="N126" s="28"/>
+      <c r="O126" s="29" t="str">
         <f aca="false">IF($M126="","",$M126*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O126" s="29" t="str">
-        <f aca="false">IF($M126="","",$M126*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P126" s="28"/>
@@ -8571,12 +8324,9 @@
       </c>
       <c r="L127" s="28"/>
       <c r="M127" s="27"/>
-      <c r="N127" s="29" t="str">
+      <c r="N127" s="28"/>
+      <c r="O127" s="29" t="str">
         <f aca="false">IF($M127="","",$M127*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O127" s="29" t="str">
-        <f aca="false">IF($M127="","",$M127*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P127" s="28"/>
@@ -8625,12 +8375,9 @@
       </c>
       <c r="L128" s="28"/>
       <c r="M128" s="27"/>
-      <c r="N128" s="29" t="str">
+      <c r="N128" s="28"/>
+      <c r="O128" s="29" t="str">
         <f aca="false">IF($M128="","",$M128*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O128" s="29" t="str">
-        <f aca="false">IF($M128="","",$M128*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P128" s="28"/>
@@ -8679,12 +8426,9 @@
       </c>
       <c r="L129" s="28"/>
       <c r="M129" s="27"/>
-      <c r="N129" s="29" t="str">
+      <c r="N129" s="28"/>
+      <c r="O129" s="29" t="str">
         <f aca="false">IF($M129="","",$M129*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O129" s="29" t="str">
-        <f aca="false">IF($M129="","",$M129*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P129" s="28"/>
@@ -8733,12 +8477,9 @@
       </c>
       <c r="L130" s="28"/>
       <c r="M130" s="27"/>
-      <c r="N130" s="29" t="str">
+      <c r="N130" s="28"/>
+      <c r="O130" s="29" t="str">
         <f aca="false">IF($M130="","",$M130*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O130" s="29" t="str">
-        <f aca="false">IF($M130="","",$M130*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P130" s="28"/>
@@ -8787,12 +8528,9 @@
       </c>
       <c r="L131" s="28"/>
       <c r="M131" s="27"/>
-      <c r="N131" s="29" t="str">
+      <c r="N131" s="28"/>
+      <c r="O131" s="29" t="str">
         <f aca="false">IF($M131="","",$M131*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O131" s="29" t="str">
-        <f aca="false">IF($M131="","",$M131*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P131" s="28"/>
@@ -8841,12 +8579,9 @@
       </c>
       <c r="L132" s="28"/>
       <c r="M132" s="27"/>
-      <c r="N132" s="29" t="str">
+      <c r="N132" s="28"/>
+      <c r="O132" s="29" t="str">
         <f aca="false">IF($M132="","",$M132*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O132" s="29" t="str">
-        <f aca="false">IF($M132="","",$M132*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P132" s="28"/>
@@ -8895,12 +8630,9 @@
       </c>
       <c r="L133" s="28"/>
       <c r="M133" s="27"/>
-      <c r="N133" s="29" t="str">
+      <c r="N133" s="28"/>
+      <c r="O133" s="29" t="str">
         <f aca="false">IF($M133="","",$M133*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O133" s="29" t="str">
-        <f aca="false">IF($M133="","",$M133*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P133" s="28"/>
@@ -8949,12 +8681,9 @@
       </c>
       <c r="L134" s="28"/>
       <c r="M134" s="27"/>
-      <c r="N134" s="29" t="str">
+      <c r="N134" s="28"/>
+      <c r="O134" s="29" t="str">
         <f aca="false">IF($M134="","",$M134*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O134" s="29" t="str">
-        <f aca="false">IF($M134="","",$M134*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P134" s="28"/>
@@ -9003,12 +8732,9 @@
       </c>
       <c r="L135" s="28"/>
       <c r="M135" s="27"/>
-      <c r="N135" s="29" t="str">
+      <c r="N135" s="28"/>
+      <c r="O135" s="29" t="str">
         <f aca="false">IF($M135="","",$M135*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O135" s="29" t="str">
-        <f aca="false">IF($M135="","",$M135*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P135" s="28"/>
@@ -9057,12 +8783,9 @@
       </c>
       <c r="L136" s="28"/>
       <c r="M136" s="27"/>
-      <c r="N136" s="29" t="str">
+      <c r="N136" s="28"/>
+      <c r="O136" s="29" t="str">
         <f aca="false">IF($M136="","",$M136*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O136" s="29" t="str">
-        <f aca="false">IF($M136="","",$M136*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P136" s="28"/>
@@ -9111,12 +8834,9 @@
       </c>
       <c r="L137" s="28"/>
       <c r="M137" s="27"/>
-      <c r="N137" s="29" t="str">
+      <c r="N137" s="28"/>
+      <c r="O137" s="29" t="str">
         <f aca="false">IF($M137="","",$M137*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O137" s="29" t="str">
-        <f aca="false">IF($M137="","",$M137*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P137" s="28"/>
@@ -9165,12 +8885,9 @@
       </c>
       <c r="L138" s="28"/>
       <c r="M138" s="27"/>
-      <c r="N138" s="29" t="str">
+      <c r="N138" s="28"/>
+      <c r="O138" s="29" t="str">
         <f aca="false">IF($M138="","",$M138*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O138" s="29" t="str">
-        <f aca="false">IF($M138="","",$M138*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P138" s="28"/>
@@ -9219,12 +8936,9 @@
       </c>
       <c r="L139" s="28"/>
       <c r="M139" s="27"/>
-      <c r="N139" s="29" t="str">
+      <c r="N139" s="28"/>
+      <c r="O139" s="29" t="str">
         <f aca="false">IF($M139="","",$M139*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O139" s="29" t="str">
-        <f aca="false">IF($M139="","",$M139*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P139" s="28"/>
@@ -9273,12 +8987,9 @@
       </c>
       <c r="L140" s="28"/>
       <c r="M140" s="27"/>
-      <c r="N140" s="29" t="str">
+      <c r="N140" s="28"/>
+      <c r="O140" s="29" t="str">
         <f aca="false">IF($M140="","",$M140*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O140" s="29" t="str">
-        <f aca="false">IF($M140="","",$M140*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P140" s="28"/>
@@ -9327,12 +9038,9 @@
       </c>
       <c r="L141" s="28"/>
       <c r="M141" s="27"/>
-      <c r="N141" s="29" t="str">
+      <c r="N141" s="28"/>
+      <c r="O141" s="29" t="str">
         <f aca="false">IF($M141="","",$M141*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O141" s="29" t="str">
-        <f aca="false">IF($M141="","",$M141*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P141" s="28"/>
@@ -9381,12 +9089,9 @@
       </c>
       <c r="L142" s="28"/>
       <c r="M142" s="27"/>
-      <c r="N142" s="29" t="str">
+      <c r="N142" s="28"/>
+      <c r="O142" s="29" t="str">
         <f aca="false">IF($M142="","",$M142*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O142" s="29" t="str">
-        <f aca="false">IF($M142="","",$M142*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P142" s="28"/>
@@ -9435,12 +9140,9 @@
       </c>
       <c r="L143" s="28"/>
       <c r="M143" s="27"/>
-      <c r="N143" s="29" t="str">
+      <c r="N143" s="28"/>
+      <c r="O143" s="29" t="str">
         <f aca="false">IF($M143="","",$M143*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O143" s="29" t="str">
-        <f aca="false">IF($M143="","",$M143*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P143" s="28"/>
@@ -9489,12 +9191,9 @@
       </c>
       <c r="L144" s="28"/>
       <c r="M144" s="27"/>
-      <c r="N144" s="29" t="str">
+      <c r="N144" s="28"/>
+      <c r="O144" s="29" t="str">
         <f aca="false">IF($M144="","",$M144*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O144" s="29" t="str">
-        <f aca="false">IF($M144="","",$M144*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P144" s="28"/>
@@ -9543,12 +9242,9 @@
       </c>
       <c r="L145" s="28"/>
       <c r="M145" s="27"/>
-      <c r="N145" s="29" t="str">
+      <c r="N145" s="28"/>
+      <c r="O145" s="29" t="str">
         <f aca="false">IF($M145="","",$M145*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O145" s="29" t="str">
-        <f aca="false">IF($M145="","",$M145*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P145" s="28"/>
@@ -9597,12 +9293,9 @@
       </c>
       <c r="L146" s="28"/>
       <c r="M146" s="27"/>
-      <c r="N146" s="29" t="str">
+      <c r="N146" s="28"/>
+      <c r="O146" s="29" t="str">
         <f aca="false">IF($M146="","",$M146*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O146" s="29" t="str">
-        <f aca="false">IF($M146="","",$M146*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P146" s="28"/>
@@ -9651,12 +9344,9 @@
       </c>
       <c r="L147" s="28"/>
       <c r="M147" s="27"/>
-      <c r="N147" s="29" t="str">
+      <c r="N147" s="28"/>
+      <c r="O147" s="29" t="str">
         <f aca="false">IF($M147="","",$M147*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O147" s="29" t="str">
-        <f aca="false">IF($M147="","",$M147*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P147" s="28"/>
@@ -9705,12 +9395,9 @@
       </c>
       <c r="L148" s="28"/>
       <c r="M148" s="27"/>
-      <c r="N148" s="29" t="str">
+      <c r="N148" s="28"/>
+      <c r="O148" s="29" t="str">
         <f aca="false">IF($M148="","",$M148*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O148" s="29" t="str">
-        <f aca="false">IF($M148="","",$M148*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P148" s="28"/>
@@ -9759,12 +9446,9 @@
       </c>
       <c r="L149" s="28"/>
       <c r="M149" s="27"/>
-      <c r="N149" s="29" t="str">
+      <c r="N149" s="28"/>
+      <c r="O149" s="29" t="str">
         <f aca="false">IF($M149="","",$M149*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O149" s="29" t="str">
-        <f aca="false">IF($M149="","",$M149*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P149" s="28"/>
@@ -9813,12 +9497,9 @@
       </c>
       <c r="L150" s="28"/>
       <c r="M150" s="27"/>
-      <c r="N150" s="29" t="str">
+      <c r="N150" s="28"/>
+      <c r="O150" s="29" t="str">
         <f aca="false">IF($M150="","",$M150*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O150" s="29" t="str">
-        <f aca="false">IF($M150="","",$M150*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P150" s="28"/>
@@ -9867,12 +9548,9 @@
       </c>
       <c r="L151" s="28"/>
       <c r="M151" s="27"/>
-      <c r="N151" s="29" t="str">
+      <c r="N151" s="28"/>
+      <c r="O151" s="29" t="str">
         <f aca="false">IF($M151="","",$M151*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O151" s="29" t="str">
-        <f aca="false">IF($M151="","",$M151*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P151" s="28"/>
@@ -9921,12 +9599,9 @@
       </c>
       <c r="L152" s="28"/>
       <c r="M152" s="27"/>
-      <c r="N152" s="29" t="str">
+      <c r="N152" s="28"/>
+      <c r="O152" s="29" t="str">
         <f aca="false">IF($M152="","",$M152*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O152" s="29" t="str">
-        <f aca="false">IF($M152="","",$M152*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P152" s="28"/>
@@ -9975,12 +9650,9 @@
       </c>
       <c r="L153" s="28"/>
       <c r="M153" s="27"/>
-      <c r="N153" s="29" t="str">
+      <c r="N153" s="28"/>
+      <c r="O153" s="29" t="str">
         <f aca="false">IF($M153="","",$M153*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O153" s="29" t="str">
-        <f aca="false">IF($M153="","",$M153*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P153" s="28"/>
@@ -10029,12 +9701,9 @@
       </c>
       <c r="L154" s="28"/>
       <c r="M154" s="27"/>
-      <c r="N154" s="29" t="str">
+      <c r="N154" s="28"/>
+      <c r="O154" s="29" t="str">
         <f aca="false">IF($M154="","",$M154*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O154" s="29" t="str">
-        <f aca="false">IF($M154="","",$M154*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P154" s="28"/>
@@ -10083,12 +9752,9 @@
       </c>
       <c r="L155" s="28"/>
       <c r="M155" s="27"/>
-      <c r="N155" s="29" t="str">
+      <c r="N155" s="28"/>
+      <c r="O155" s="29" t="str">
         <f aca="false">IF($M155="","",$M155*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O155" s="29" t="str">
-        <f aca="false">IF($M155="","",$M155*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P155" s="28"/>
@@ -10137,12 +9803,9 @@
       </c>
       <c r="L156" s="28"/>
       <c r="M156" s="27"/>
-      <c r="N156" s="29" t="str">
+      <c r="N156" s="28"/>
+      <c r="O156" s="29" t="str">
         <f aca="false">IF($M156="","",$M156*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O156" s="29" t="str">
-        <f aca="false">IF($M156="","",$M156*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P156" s="28"/>
@@ -10191,12 +9854,9 @@
       </c>
       <c r="L157" s="28"/>
       <c r="M157" s="27"/>
-      <c r="N157" s="29" t="str">
+      <c r="N157" s="28"/>
+      <c r="O157" s="29" t="str">
         <f aca="false">IF($M157="","",$M157*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O157" s="29" t="str">
-        <f aca="false">IF($M157="","",$M157*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P157" s="28"/>
@@ -10245,12 +9905,9 @@
       </c>
       <c r="L158" s="28"/>
       <c r="M158" s="27"/>
-      <c r="N158" s="29" t="str">
+      <c r="N158" s="28"/>
+      <c r="O158" s="29" t="str">
         <f aca="false">IF($M158="","",$M158*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O158" s="29" t="str">
-        <f aca="false">IF($M158="","",$M158*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P158" s="28"/>
@@ -10299,12 +9956,9 @@
       </c>
       <c r="L159" s="28"/>
       <c r="M159" s="27"/>
-      <c r="N159" s="29" t="str">
+      <c r="N159" s="28"/>
+      <c r="O159" s="29" t="str">
         <f aca="false">IF($M159="","",$M159*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O159" s="29" t="str">
-        <f aca="false">IF($M159="","",$M159*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P159" s="28"/>
@@ -10353,12 +10007,9 @@
       </c>
       <c r="L160" s="28"/>
       <c r="M160" s="27"/>
-      <c r="N160" s="29" t="str">
+      <c r="N160" s="28"/>
+      <c r="O160" s="29" t="str">
         <f aca="false">IF($M160="","",$M160*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O160" s="29" t="str">
-        <f aca="false">IF($M160="","",$M160*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P160" s="28"/>
@@ -10407,12 +10058,9 @@
       </c>
       <c r="L161" s="28"/>
       <c r="M161" s="27"/>
-      <c r="N161" s="29" t="str">
+      <c r="N161" s="28"/>
+      <c r="O161" s="29" t="str">
         <f aca="false">IF($M161="","",$M161*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O161" s="29" t="str">
-        <f aca="false">IF($M161="","",$M161*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P161" s="28"/>
@@ -10461,12 +10109,9 @@
       </c>
       <c r="L162" s="28"/>
       <c r="M162" s="27"/>
-      <c r="N162" s="29" t="str">
+      <c r="N162" s="28"/>
+      <c r="O162" s="29" t="str">
         <f aca="false">IF($M162="","",$M162*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O162" s="29" t="str">
-        <f aca="false">IF($M162="","",$M162*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P162" s="28"/>
@@ -10515,12 +10160,9 @@
       </c>
       <c r="L163" s="28"/>
       <c r="M163" s="27"/>
-      <c r="N163" s="29" t="str">
+      <c r="N163" s="28"/>
+      <c r="O163" s="29" t="str">
         <f aca="false">IF($M163="","",$M163*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O163" s="29" t="str">
-        <f aca="false">IF($M163="","",$M163*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P163" s="28"/>
@@ -10569,12 +10211,9 @@
       </c>
       <c r="L164" s="28"/>
       <c r="M164" s="27"/>
-      <c r="N164" s="29" t="str">
+      <c r="N164" s="28"/>
+      <c r="O164" s="29" t="str">
         <f aca="false">IF($M164="","",$M164*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O164" s="29" t="str">
-        <f aca="false">IF($M164="","",$M164*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P164" s="28"/>
@@ -10623,12 +10262,9 @@
       </c>
       <c r="L165" s="28"/>
       <c r="M165" s="27"/>
-      <c r="N165" s="29" t="str">
+      <c r="N165" s="28"/>
+      <c r="O165" s="29" t="str">
         <f aca="false">IF($M165="","",$M165*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O165" s="29" t="str">
-        <f aca="false">IF($M165="","",$M165*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P165" s="28"/>
@@ -10677,12 +10313,9 @@
       </c>
       <c r="L166" s="28"/>
       <c r="M166" s="27"/>
-      <c r="N166" s="29" t="str">
+      <c r="N166" s="28"/>
+      <c r="O166" s="29" t="str">
         <f aca="false">IF($M166="","",$M166*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O166" s="29" t="str">
-        <f aca="false">IF($M166="","",$M166*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P166" s="28"/>
@@ -10731,12 +10364,9 @@
       </c>
       <c r="L167" s="28"/>
       <c r="M167" s="27"/>
-      <c r="N167" s="29" t="str">
+      <c r="N167" s="28"/>
+      <c r="O167" s="29" t="str">
         <f aca="false">IF($M167="","",$M167*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O167" s="29" t="str">
-        <f aca="false">IF($M167="","",$M167*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P167" s="28"/>
@@ -10785,12 +10415,9 @@
       </c>
       <c r="L168" s="28"/>
       <c r="M168" s="27"/>
-      <c r="N168" s="29" t="str">
+      <c r="N168" s="28"/>
+      <c r="O168" s="29" t="str">
         <f aca="false">IF($M168="","",$M168*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O168" s="29" t="str">
-        <f aca="false">IF($M168="","",$M168*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P168" s="28"/>
@@ -10839,12 +10466,9 @@
       </c>
       <c r="L169" s="28"/>
       <c r="M169" s="27"/>
-      <c r="N169" s="29" t="str">
+      <c r="N169" s="28"/>
+      <c r="O169" s="29" t="str">
         <f aca="false">IF($M169="","",$M169*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O169" s="29" t="str">
-        <f aca="false">IF($M169="","",$M169*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P169" s="28"/>
@@ -10893,12 +10517,9 @@
       </c>
       <c r="L170" s="28"/>
       <c r="M170" s="27"/>
-      <c r="N170" s="29" t="str">
+      <c r="N170" s="28"/>
+      <c r="O170" s="29" t="str">
         <f aca="false">IF($M170="","",$M170*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O170" s="29" t="str">
-        <f aca="false">IF($M170="","",$M170*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P170" s="28"/>
@@ -10947,12 +10568,9 @@
       </c>
       <c r="L171" s="28"/>
       <c r="M171" s="27"/>
-      <c r="N171" s="29" t="str">
+      <c r="N171" s="28"/>
+      <c r="O171" s="29" t="str">
         <f aca="false">IF($M171="","",$M171*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O171" s="29" t="str">
-        <f aca="false">IF($M171="","",$M171*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P171" s="28"/>
@@ -11001,12 +10619,9 @@
       </c>
       <c r="L172" s="28"/>
       <c r="M172" s="27"/>
-      <c r="N172" s="29" t="str">
+      <c r="N172" s="28"/>
+      <c r="O172" s="29" t="str">
         <f aca="false">IF($M172="","",$M172*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O172" s="29" t="str">
-        <f aca="false">IF($M172="","",$M172*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P172" s="28"/>
@@ -11055,12 +10670,9 @@
       </c>
       <c r="L173" s="28"/>
       <c r="M173" s="27"/>
-      <c r="N173" s="29" t="str">
+      <c r="N173" s="28"/>
+      <c r="O173" s="29" t="str">
         <f aca="false">IF($M173="","",$M173*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O173" s="29" t="str">
-        <f aca="false">IF($M173="","",$M173*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P173" s="28"/>
@@ -11109,12 +10721,9 @@
       </c>
       <c r="L174" s="28"/>
       <c r="M174" s="27"/>
-      <c r="N174" s="29" t="str">
+      <c r="N174" s="28"/>
+      <c r="O174" s="29" t="str">
         <f aca="false">IF($M174="","",$M174*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O174" s="29" t="str">
-        <f aca="false">IF($M174="","",$M174*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P174" s="28"/>
@@ -11163,12 +10772,9 @@
       </c>
       <c r="L175" s="28"/>
       <c r="M175" s="27"/>
-      <c r="N175" s="29" t="str">
+      <c r="N175" s="28"/>
+      <c r="O175" s="29" t="str">
         <f aca="false">IF($M175="","",$M175*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O175" s="29" t="str">
-        <f aca="false">IF($M175="","",$M175*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P175" s="28"/>
@@ -11217,12 +10823,9 @@
       </c>
       <c r="L176" s="28"/>
       <c r="M176" s="27"/>
-      <c r="N176" s="29" t="str">
+      <c r="N176" s="28"/>
+      <c r="O176" s="29" t="str">
         <f aca="false">IF($M176="","",$M176*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O176" s="29" t="str">
-        <f aca="false">IF($M176="","",$M176*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P176" s="28"/>
@@ -11271,12 +10874,9 @@
       </c>
       <c r="L177" s="28"/>
       <c r="M177" s="27"/>
-      <c r="N177" s="29" t="str">
+      <c r="N177" s="28"/>
+      <c r="O177" s="29" t="str">
         <f aca="false">IF($M177="","",$M177*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O177" s="29" t="str">
-        <f aca="false">IF($M177="","",$M177*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P177" s="28"/>
@@ -11325,12 +10925,9 @@
       </c>
       <c r="L178" s="28"/>
       <c r="M178" s="27"/>
-      <c r="N178" s="29" t="str">
+      <c r="N178" s="28"/>
+      <c r="O178" s="29" t="str">
         <f aca="false">IF($M178="","",$M178*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O178" s="29" t="str">
-        <f aca="false">IF($M178="","",$M178*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P178" s="28"/>
@@ -11379,12 +10976,9 @@
       </c>
       <c r="L179" s="28"/>
       <c r="M179" s="27"/>
-      <c r="N179" s="29" t="str">
+      <c r="N179" s="28"/>
+      <c r="O179" s="29" t="str">
         <f aca="false">IF($M179="","",$M179*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O179" s="29" t="str">
-        <f aca="false">IF($M179="","",$M179*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P179" s="28"/>
@@ -11433,12 +11027,9 @@
       </c>
       <c r="L180" s="28"/>
       <c r="M180" s="27"/>
-      <c r="N180" s="29" t="str">
+      <c r="N180" s="28"/>
+      <c r="O180" s="29" t="str">
         <f aca="false">IF($M180="","",$M180*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O180" s="29" t="str">
-        <f aca="false">IF($M180="","",$M180*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P180" s="28"/>
@@ -11487,12 +11078,9 @@
       </c>
       <c r="L181" s="28"/>
       <c r="M181" s="27"/>
-      <c r="N181" s="29" t="str">
+      <c r="N181" s="28"/>
+      <c r="O181" s="29" t="str">
         <f aca="false">IF($M181="","",$M181*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O181" s="29" t="str">
-        <f aca="false">IF($M181="","",$M181*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P181" s="28"/>
@@ -11541,12 +11129,9 @@
       </c>
       <c r="L182" s="28"/>
       <c r="M182" s="27"/>
-      <c r="N182" s="29" t="str">
+      <c r="N182" s="28"/>
+      <c r="O182" s="29" t="str">
         <f aca="false">IF($M182="","",$M182*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O182" s="29" t="str">
-        <f aca="false">IF($M182="","",$M182*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P182" s="28"/>
@@ -11595,12 +11180,9 @@
       </c>
       <c r="L183" s="28"/>
       <c r="M183" s="27"/>
-      <c r="N183" s="29" t="str">
+      <c r="N183" s="28"/>
+      <c r="O183" s="29" t="str">
         <f aca="false">IF($M183="","",$M183*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O183" s="29" t="str">
-        <f aca="false">IF($M183="","",$M183*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P183" s="28"/>
@@ -11649,12 +11231,9 @@
       </c>
       <c r="L184" s="28"/>
       <c r="M184" s="27"/>
-      <c r="N184" s="29" t="str">
+      <c r="N184" s="28"/>
+      <c r="O184" s="29" t="str">
         <f aca="false">IF($M184="","",$M184*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O184" s="29" t="str">
-        <f aca="false">IF($M184="","",$M184*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P184" s="28"/>
@@ -11703,12 +11282,9 @@
       </c>
       <c r="L185" s="28"/>
       <c r="M185" s="27"/>
-      <c r="N185" s="29" t="str">
+      <c r="N185" s="28"/>
+      <c r="O185" s="29" t="str">
         <f aca="false">IF($M185="","",$M185*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O185" s="29" t="str">
-        <f aca="false">IF($M185="","",$M185*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P185" s="28"/>
@@ -11757,12 +11333,9 @@
       </c>
       <c r="L186" s="28"/>
       <c r="M186" s="27"/>
-      <c r="N186" s="29" t="str">
+      <c r="N186" s="28"/>
+      <c r="O186" s="29" t="str">
         <f aca="false">IF($M186="","",$M186*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O186" s="29" t="str">
-        <f aca="false">IF($M186="","",$M186*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P186" s="28"/>
@@ -11811,12 +11384,9 @@
       </c>
       <c r="L187" s="28"/>
       <c r="M187" s="27"/>
-      <c r="N187" s="29" t="str">
+      <c r="N187" s="28"/>
+      <c r="O187" s="29" t="str">
         <f aca="false">IF($M187="","",$M187*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O187" s="29" t="str">
-        <f aca="false">IF($M187="","",$M187*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P187" s="28"/>
@@ -11865,12 +11435,9 @@
       </c>
       <c r="L188" s="28"/>
       <c r="M188" s="27"/>
-      <c r="N188" s="29" t="str">
+      <c r="N188" s="28"/>
+      <c r="O188" s="29" t="str">
         <f aca="false">IF($M188="","",$M188*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O188" s="29" t="str">
-        <f aca="false">IF($M188="","",$M188*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P188" s="28"/>
@@ -11919,12 +11486,9 @@
       </c>
       <c r="L189" s="28"/>
       <c r="M189" s="27"/>
-      <c r="N189" s="29" t="str">
+      <c r="N189" s="28"/>
+      <c r="O189" s="29" t="str">
         <f aca="false">IF($M189="","",$M189*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O189" s="29" t="str">
-        <f aca="false">IF($M189="","",$M189*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P189" s="28"/>
@@ -11973,12 +11537,9 @@
       </c>
       <c r="L190" s="28"/>
       <c r="M190" s="27"/>
-      <c r="N190" s="29" t="str">
+      <c r="N190" s="28"/>
+      <c r="O190" s="29" t="str">
         <f aca="false">IF($M190="","",$M190*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O190" s="29" t="str">
-        <f aca="false">IF($M190="","",$M190*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P190" s="28"/>
@@ -12027,12 +11588,9 @@
       </c>
       <c r="L191" s="28"/>
       <c r="M191" s="27"/>
-      <c r="N191" s="29" t="str">
+      <c r="N191" s="28"/>
+      <c r="O191" s="29" t="str">
         <f aca="false">IF($M191="","",$M191*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O191" s="29" t="str">
-        <f aca="false">IF($M191="","",$M191*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P191" s="28"/>
@@ -12081,12 +11639,9 @@
       </c>
       <c r="L192" s="28"/>
       <c r="M192" s="27"/>
-      <c r="N192" s="29" t="str">
+      <c r="N192" s="28"/>
+      <c r="O192" s="29" t="str">
         <f aca="false">IF($M192="","",$M192*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O192" s="29" t="str">
-        <f aca="false">IF($M192="","",$M192*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P192" s="28"/>
@@ -12135,12 +11690,9 @@
       </c>
       <c r="L193" s="28"/>
       <c r="M193" s="27"/>
-      <c r="N193" s="29" t="str">
+      <c r="N193" s="28"/>
+      <c r="O193" s="29" t="str">
         <f aca="false">IF($M193="","",$M193*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O193" s="29" t="str">
-        <f aca="false">IF($M193="","",$M193*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P193" s="28"/>
@@ -12189,12 +11741,9 @@
       </c>
       <c r="L194" s="28"/>
       <c r="M194" s="27"/>
-      <c r="N194" s="29" t="str">
+      <c r="N194" s="28"/>
+      <c r="O194" s="29" t="str">
         <f aca="false">IF($M194="","",$M194*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O194" s="29" t="str">
-        <f aca="false">IF($M194="","",$M194*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P194" s="28"/>
@@ -12243,12 +11792,9 @@
       </c>
       <c r="L195" s="28"/>
       <c r="M195" s="27"/>
-      <c r="N195" s="29" t="str">
+      <c r="N195" s="28"/>
+      <c r="O195" s="29" t="str">
         <f aca="false">IF($M195="","",$M195*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O195" s="29" t="str">
-        <f aca="false">IF($M195="","",$M195*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P195" s="28"/>
@@ -12297,12 +11843,9 @@
       </c>
       <c r="L196" s="28"/>
       <c r="M196" s="27"/>
-      <c r="N196" s="29" t="str">
+      <c r="N196" s="28"/>
+      <c r="O196" s="29" t="str">
         <f aca="false">IF($M196="","",$M196*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O196" s="29" t="str">
-        <f aca="false">IF($M196="","",$M196*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P196" s="28"/>
@@ -12351,12 +11894,9 @@
       </c>
       <c r="L197" s="28"/>
       <c r="M197" s="27"/>
-      <c r="N197" s="29" t="str">
+      <c r="N197" s="28"/>
+      <c r="O197" s="29" t="str">
         <f aca="false">IF($M197="","",$M197*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O197" s="29" t="str">
-        <f aca="false">IF($M197="","",$M197*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P197" s="28"/>
@@ -12405,12 +11945,9 @@
       </c>
       <c r="L198" s="28"/>
       <c r="M198" s="27"/>
-      <c r="N198" s="29" t="str">
+      <c r="N198" s="28"/>
+      <c r="O198" s="29" t="str">
         <f aca="false">IF($M198="","",$M198*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O198" s="29" t="str">
-        <f aca="false">IF($M198="","",$M198*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P198" s="28"/>
@@ -12459,12 +11996,9 @@
       </c>
       <c r="L199" s="28"/>
       <c r="M199" s="27"/>
-      <c r="N199" s="29" t="str">
+      <c r="N199" s="28"/>
+      <c r="O199" s="29" t="str">
         <f aca="false">IF($M199="","",$M199*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O199" s="29" t="str">
-        <f aca="false">IF($M199="","",$M199*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P199" s="28"/>
@@ -12513,12 +12047,9 @@
       </c>
       <c r="L200" s="28"/>
       <c r="M200" s="27"/>
-      <c r="N200" s="29" t="str">
+      <c r="N200" s="28"/>
+      <c r="O200" s="29" t="str">
         <f aca="false">IF($M200="","",$M200*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O200" s="29" t="str">
-        <f aca="false">IF($M200="","",$M200*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P200" s="28"/>
@@ -12567,12 +12098,9 @@
       </c>
       <c r="L201" s="28"/>
       <c r="M201" s="27"/>
-      <c r="N201" s="29" t="str">
+      <c r="N201" s="28"/>
+      <c r="O201" s="29" t="str">
         <f aca="false">IF($M201="","",$M201*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O201" s="29" t="str">
-        <f aca="false">IF($M201="","",$M201*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P201" s="28"/>
@@ -12621,12 +12149,9 @@
       </c>
       <c r="L202" s="28"/>
       <c r="M202" s="27"/>
-      <c r="N202" s="29" t="str">
+      <c r="N202" s="28"/>
+      <c r="O202" s="29" t="str">
         <f aca="false">IF($M202="","",$M202*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O202" s="29" t="str">
-        <f aca="false">IF($M202="","",$M202*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P202" s="28"/>
@@ -12675,12 +12200,9 @@
       </c>
       <c r="L203" s="28"/>
       <c r="M203" s="27"/>
-      <c r="N203" s="29" t="str">
+      <c r="N203" s="28"/>
+      <c r="O203" s="29" t="str">
         <f aca="false">IF($M203="","",$M203*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O203" s="29" t="str">
-        <f aca="false">IF($M203="","",$M203*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P203" s="28"/>
@@ -12729,12 +12251,9 @@
       </c>
       <c r="L204" s="28"/>
       <c r="M204" s="27"/>
-      <c r="N204" s="29" t="str">
+      <c r="N204" s="28"/>
+      <c r="O204" s="29" t="str">
         <f aca="false">IF($M204="","",$M204*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O204" s="29" t="str">
-        <f aca="false">IF($M204="","",$M204*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P204" s="28"/>
@@ -12783,12 +12302,9 @@
       </c>
       <c r="L205" s="28"/>
       <c r="M205" s="27"/>
-      <c r="N205" s="29" t="str">
+      <c r="N205" s="28"/>
+      <c r="O205" s="29" t="str">
         <f aca="false">IF($M205="","",$M205*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O205" s="29" t="str">
-        <f aca="false">IF($M205="","",$M205*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P205" s="28"/>
@@ -12837,12 +12353,9 @@
       </c>
       <c r="L206" s="28"/>
       <c r="M206" s="27"/>
-      <c r="N206" s="29" t="str">
+      <c r="N206" s="28"/>
+      <c r="O206" s="29" t="str">
         <f aca="false">IF($M206="","",$M206*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O206" s="29" t="str">
-        <f aca="false">IF($M206="","",$M206*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P206" s="28"/>
@@ -12891,12 +12404,9 @@
       </c>
       <c r="L207" s="28"/>
       <c r="M207" s="27"/>
-      <c r="N207" s="29" t="str">
+      <c r="N207" s="28"/>
+      <c r="O207" s="29" t="str">
         <f aca="false">IF($M207="","",$M207*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O207" s="29" t="str">
-        <f aca="false">IF($M207="","",$M207*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P207" s="28"/>
@@ -12945,12 +12455,9 @@
       </c>
       <c r="L208" s="28"/>
       <c r="M208" s="27"/>
-      <c r="N208" s="29" t="str">
+      <c r="N208" s="28"/>
+      <c r="O208" s="29" t="str">
         <f aca="false">IF($M208="","",$M208*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O208" s="29" t="str">
-        <f aca="false">IF($M208="","",$M208*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P208" s="28"/>
@@ -12999,12 +12506,9 @@
       </c>
       <c r="L209" s="28"/>
       <c r="M209" s="27"/>
-      <c r="N209" s="29" t="str">
+      <c r="N209" s="28"/>
+      <c r="O209" s="29" t="str">
         <f aca="false">IF($M209="","",$M209*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O209" s="29" t="str">
-        <f aca="false">IF($M209="","",$M209*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P209" s="28"/>
@@ -13053,12 +12557,9 @@
       </c>
       <c r="L210" s="28"/>
       <c r="M210" s="27"/>
-      <c r="N210" s="29" t="str">
+      <c r="N210" s="28"/>
+      <c r="O210" s="29" t="str">
         <f aca="false">IF($M210="","",$M210*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O210" s="29" t="str">
-        <f aca="false">IF($M210="","",$M210*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P210" s="28"/>
@@ -13107,12 +12608,9 @@
       </c>
       <c r="L211" s="28"/>
       <c r="M211" s="27"/>
-      <c r="N211" s="29" t="str">
+      <c r="N211" s="28"/>
+      <c r="O211" s="29" t="str">
         <f aca="false">IF($M211="","",$M211*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O211" s="29" t="str">
-        <f aca="false">IF($M211="","",$M211*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P211" s="28"/>
@@ -13161,12 +12659,9 @@
       </c>
       <c r="L212" s="28"/>
       <c r="M212" s="27"/>
-      <c r="N212" s="29" t="str">
+      <c r="N212" s="28"/>
+      <c r="O212" s="29" t="str">
         <f aca="false">IF($M212="","",$M212*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O212" s="29" t="str">
-        <f aca="false">IF($M212="","",$M212*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P212" s="28"/>
@@ -13215,12 +12710,9 @@
       </c>
       <c r="L213" s="28"/>
       <c r="M213" s="27"/>
-      <c r="N213" s="29" t="str">
+      <c r="N213" s="28"/>
+      <c r="O213" s="29" t="str">
         <f aca="false">IF($M213="","",$M213*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O213" s="29" t="str">
-        <f aca="false">IF($M213="","",$M213*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P213" s="28"/>
@@ -13269,12 +12761,9 @@
       </c>
       <c r="L214" s="28"/>
       <c r="M214" s="27"/>
-      <c r="N214" s="29" t="str">
+      <c r="N214" s="28"/>
+      <c r="O214" s="29" t="str">
         <f aca="false">IF($M214="","",$M214*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O214" s="29" t="str">
-        <f aca="false">IF($M214="","",$M214*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P214" s="28"/>
@@ -13323,12 +12812,9 @@
       </c>
       <c r="L215" s="28"/>
       <c r="M215" s="27"/>
-      <c r="N215" s="29" t="str">
+      <c r="N215" s="28"/>
+      <c r="O215" s="29" t="str">
         <f aca="false">IF($M215="","",$M215*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O215" s="29" t="str">
-        <f aca="false">IF($M215="","",$M215*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P215" s="28"/>
@@ -13377,12 +12863,9 @@
       </c>
       <c r="L216" s="28"/>
       <c r="M216" s="27"/>
-      <c r="N216" s="29" t="str">
+      <c r="N216" s="28"/>
+      <c r="O216" s="29" t="str">
         <f aca="false">IF($M216="","",$M216*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O216" s="29" t="str">
-        <f aca="false">IF($M216="","",$M216*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P216" s="28"/>
@@ -13431,12 +12914,9 @@
       </c>
       <c r="L217" s="28"/>
       <c r="M217" s="27"/>
-      <c r="N217" s="29" t="str">
+      <c r="N217" s="28"/>
+      <c r="O217" s="29" t="str">
         <f aca="false">IF($M217="","",$M217*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O217" s="29" t="str">
-        <f aca="false">IF($M217="","",$M217*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P217" s="28"/>
@@ -13485,12 +12965,9 @@
       </c>
       <c r="L218" s="28"/>
       <c r="M218" s="27"/>
-      <c r="N218" s="29" t="str">
+      <c r="N218" s="28"/>
+      <c r="O218" s="29" t="str">
         <f aca="false">IF($M218="","",$M218*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O218" s="29" t="str">
-        <f aca="false">IF($M218="","",$M218*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P218" s="28"/>
@@ -13539,12 +13016,9 @@
       </c>
       <c r="L219" s="28"/>
       <c r="M219" s="27"/>
-      <c r="N219" s="29" t="str">
+      <c r="N219" s="28"/>
+      <c r="O219" s="29" t="str">
         <f aca="false">IF($M219="","",$M219*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O219" s="29" t="str">
-        <f aca="false">IF($M219="","",$M219*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P219" s="28"/>
@@ -13593,12 +13067,9 @@
       </c>
       <c r="L220" s="28"/>
       <c r="M220" s="27"/>
-      <c r="N220" s="29" t="str">
+      <c r="N220" s="28"/>
+      <c r="O220" s="29" t="str">
         <f aca="false">IF($M220="","",$M220*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O220" s="29" t="str">
-        <f aca="false">IF($M220="","",$M220*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P220" s="28"/>
@@ -13647,12 +13118,9 @@
       </c>
       <c r="L221" s="28"/>
       <c r="M221" s="27"/>
-      <c r="N221" s="29" t="str">
+      <c r="N221" s="28"/>
+      <c r="O221" s="29" t="str">
         <f aca="false">IF($M221="","",$M221*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O221" s="29" t="str">
-        <f aca="false">IF($M221="","",$M221*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P221" s="28"/>
@@ -13701,12 +13169,9 @@
       </c>
       <c r="L222" s="28"/>
       <c r="M222" s="27"/>
-      <c r="N222" s="29" t="str">
+      <c r="N222" s="28"/>
+      <c r="O222" s="29" t="str">
         <f aca="false">IF($M222="","",$M222*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O222" s="29" t="str">
-        <f aca="false">IF($M222="","",$M222*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P222" s="28"/>
@@ -13755,12 +13220,9 @@
       </c>
       <c r="L223" s="28"/>
       <c r="M223" s="27"/>
-      <c r="N223" s="29" t="str">
+      <c r="N223" s="28"/>
+      <c r="O223" s="29" t="str">
         <f aca="false">IF($M223="","",$M223*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O223" s="29" t="str">
-        <f aca="false">IF($M223="","",$M223*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P223" s="28"/>
@@ -13809,12 +13271,9 @@
       </c>
       <c r="L224" s="28"/>
       <c r="M224" s="27"/>
-      <c r="N224" s="29" t="str">
+      <c r="N224" s="28"/>
+      <c r="O224" s="29" t="str">
         <f aca="false">IF($M224="","",$M224*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O224" s="29" t="str">
-        <f aca="false">IF($M224="","",$M224*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P224" s="28"/>
@@ -13863,12 +13322,9 @@
       </c>
       <c r="L225" s="28"/>
       <c r="M225" s="27"/>
-      <c r="N225" s="29" t="str">
+      <c r="N225" s="28"/>
+      <c r="O225" s="29" t="str">
         <f aca="false">IF($M225="","",$M225*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O225" s="29" t="str">
-        <f aca="false">IF($M225="","",$M225*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P225" s="28"/>
@@ -13917,12 +13373,9 @@
       </c>
       <c r="L226" s="28"/>
       <c r="M226" s="27"/>
-      <c r="N226" s="29" t="str">
+      <c r="N226" s="28"/>
+      <c r="O226" s="29" t="str">
         <f aca="false">IF($M226="","",$M226*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O226" s="29" t="str">
-        <f aca="false">IF($M226="","",$M226*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P226" s="28"/>
@@ -13971,12 +13424,9 @@
       </c>
       <c r="L227" s="28"/>
       <c r="M227" s="27"/>
-      <c r="N227" s="29" t="str">
+      <c r="N227" s="28"/>
+      <c r="O227" s="29" t="str">
         <f aca="false">IF($M227="","",$M227*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O227" s="29" t="str">
-        <f aca="false">IF($M227="","",$M227*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P227" s="28"/>
@@ -14025,12 +13475,9 @@
       </c>
       <c r="L228" s="28"/>
       <c r="M228" s="27"/>
-      <c r="N228" s="29" t="str">
+      <c r="N228" s="28"/>
+      <c r="O228" s="29" t="str">
         <f aca="false">IF($M228="","",$M228*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O228" s="29" t="str">
-        <f aca="false">IF($M228="","",$M228*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P228" s="28"/>
@@ -14079,12 +13526,9 @@
       </c>
       <c r="L229" s="28"/>
       <c r="M229" s="27"/>
-      <c r="N229" s="29" t="str">
+      <c r="N229" s="28"/>
+      <c r="O229" s="29" t="str">
         <f aca="false">IF($M229="","",$M229*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O229" s="29" t="str">
-        <f aca="false">IF($M229="","",$M229*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P229" s="28"/>
@@ -14133,12 +13577,9 @@
       </c>
       <c r="L230" s="28"/>
       <c r="M230" s="27"/>
-      <c r="N230" s="29" t="str">
+      <c r="N230" s="28"/>
+      <c r="O230" s="29" t="str">
         <f aca="false">IF($M230="","",$M230*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O230" s="29" t="str">
-        <f aca="false">IF($M230="","",$M230*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P230" s="28"/>
@@ -14187,12 +13628,9 @@
       </c>
       <c r="L231" s="28"/>
       <c r="M231" s="27"/>
-      <c r="N231" s="29" t="str">
+      <c r="N231" s="28"/>
+      <c r="O231" s="29" t="str">
         <f aca="false">IF($M231="","",$M231*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O231" s="29" t="str">
-        <f aca="false">IF($M231="","",$M231*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P231" s="28"/>
@@ -14241,12 +13679,9 @@
       </c>
       <c r="L232" s="28"/>
       <c r="M232" s="27"/>
-      <c r="N232" s="29" t="str">
+      <c r="N232" s="28"/>
+      <c r="O232" s="29" t="str">
         <f aca="false">IF($M232="","",$M232*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O232" s="29" t="str">
-        <f aca="false">IF($M232="","",$M232*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P232" s="28"/>
@@ -14295,12 +13730,9 @@
       </c>
       <c r="L233" s="28"/>
       <c r="M233" s="27"/>
-      <c r="N233" s="29" t="str">
+      <c r="N233" s="28"/>
+      <c r="O233" s="29" t="str">
         <f aca="false">IF($M233="","",$M233*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O233" s="29" t="str">
-        <f aca="false">IF($M233="","",$M233*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P233" s="28"/>
@@ -14349,12 +13781,9 @@
       </c>
       <c r="L234" s="28"/>
       <c r="M234" s="27"/>
-      <c r="N234" s="29" t="str">
+      <c r="N234" s="28"/>
+      <c r="O234" s="29" t="str">
         <f aca="false">IF($M234="","",$M234*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O234" s="29" t="str">
-        <f aca="false">IF($M234="","",$M234*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P234" s="28"/>
@@ -14403,12 +13832,9 @@
       </c>
       <c r="L235" s="28"/>
       <c r="M235" s="27"/>
-      <c r="N235" s="29" t="str">
+      <c r="N235" s="28"/>
+      <c r="O235" s="29" t="str">
         <f aca="false">IF($M235="","",$M235*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O235" s="29" t="str">
-        <f aca="false">IF($M235="","",$M235*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P235" s="28"/>
@@ -14457,12 +13883,9 @@
       </c>
       <c r="L236" s="28"/>
       <c r="M236" s="27"/>
-      <c r="N236" s="29" t="str">
+      <c r="N236" s="28"/>
+      <c r="O236" s="29" t="str">
         <f aca="false">IF($M236="","",$M236*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O236" s="29" t="str">
-        <f aca="false">IF($M236="","",$M236*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P236" s="28"/>
@@ -14511,12 +13934,9 @@
       </c>
       <c r="L237" s="28"/>
       <c r="M237" s="27"/>
-      <c r="N237" s="29" t="str">
+      <c r="N237" s="28"/>
+      <c r="O237" s="29" t="str">
         <f aca="false">IF($M237="","",$M237*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O237" s="29" t="str">
-        <f aca="false">IF($M237="","",$M237*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P237" s="28"/>
@@ -14565,12 +13985,9 @@
       </c>
       <c r="L238" s="28"/>
       <c r="M238" s="27"/>
-      <c r="N238" s="29" t="str">
+      <c r="N238" s="28"/>
+      <c r="O238" s="29" t="str">
         <f aca="false">IF($M238="","",$M238*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O238" s="29" t="str">
-        <f aca="false">IF($M238="","",$M238*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P238" s="28"/>
@@ -14619,12 +14036,9 @@
       </c>
       <c r="L239" s="28"/>
       <c r="M239" s="27"/>
-      <c r="N239" s="29" t="str">
+      <c r="N239" s="28"/>
+      <c r="O239" s="29" t="str">
         <f aca="false">IF($M239="","",$M239*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O239" s="29" t="str">
-        <f aca="false">IF($M239="","",$M239*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P239" s="28"/>
@@ -14673,12 +14087,9 @@
       </c>
       <c r="L240" s="28"/>
       <c r="M240" s="27"/>
-      <c r="N240" s="29" t="str">
+      <c r="N240" s="28"/>
+      <c r="O240" s="29" t="str">
         <f aca="false">IF($M240="","",$M240*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O240" s="29" t="str">
-        <f aca="false">IF($M240="","",$M240*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P240" s="28"/>
@@ -14727,12 +14138,9 @@
       </c>
       <c r="L241" s="28"/>
       <c r="M241" s="27"/>
-      <c r="N241" s="29" t="str">
+      <c r="N241" s="28"/>
+      <c r="O241" s="29" t="str">
         <f aca="false">IF($M241="","",$M241*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O241" s="29" t="str">
-        <f aca="false">IF($M241="","",$M241*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P241" s="28"/>
@@ -14781,12 +14189,9 @@
       </c>
       <c r="L242" s="28"/>
       <c r="M242" s="27"/>
-      <c r="N242" s="29" t="str">
+      <c r="N242" s="28"/>
+      <c r="O242" s="29" t="str">
         <f aca="false">IF($M242="","",$M242*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O242" s="29" t="str">
-        <f aca="false">IF($M242="","",$M242*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P242" s="28"/>
@@ -14835,12 +14240,9 @@
       </c>
       <c r="L243" s="28"/>
       <c r="M243" s="27"/>
-      <c r="N243" s="29" t="str">
+      <c r="N243" s="28"/>
+      <c r="O243" s="29" t="str">
         <f aca="false">IF($M243="","",$M243*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O243" s="29" t="str">
-        <f aca="false">IF($M243="","",$M243*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P243" s="28"/>
@@ -14889,12 +14291,9 @@
       </c>
       <c r="L244" s="28"/>
       <c r="M244" s="27"/>
-      <c r="N244" s="29" t="str">
+      <c r="N244" s="28"/>
+      <c r="O244" s="29" t="str">
         <f aca="false">IF($M244="","",$M244*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O244" s="29" t="str">
-        <f aca="false">IF($M244="","",$M244*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P244" s="28"/>
@@ -14943,12 +14342,9 @@
       </c>
       <c r="L245" s="28"/>
       <c r="M245" s="27"/>
-      <c r="N245" s="29" t="str">
+      <c r="N245" s="28"/>
+      <c r="O245" s="29" t="str">
         <f aca="false">IF($M245="","",$M245*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O245" s="29" t="str">
-        <f aca="false">IF($M245="","",$M245*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P245" s="28"/>
@@ -14997,12 +14393,9 @@
       </c>
       <c r="L246" s="28"/>
       <c r="M246" s="27"/>
-      <c r="N246" s="29" t="str">
+      <c r="N246" s="28"/>
+      <c r="O246" s="29" t="str">
         <f aca="false">IF($M246="","",$M246*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O246" s="29" t="str">
-        <f aca="false">IF($M246="","",$M246*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P246" s="28"/>
@@ -15051,12 +14444,9 @@
       </c>
       <c r="L247" s="28"/>
       <c r="M247" s="27"/>
-      <c r="N247" s="29" t="str">
+      <c r="N247" s="28"/>
+      <c r="O247" s="29" t="str">
         <f aca="false">IF($M247="","",$M247*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O247" s="29" t="str">
-        <f aca="false">IF($M247="","",$M247*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P247" s="28"/>
@@ -15105,12 +14495,9 @@
       </c>
       <c r="L248" s="28"/>
       <c r="M248" s="27"/>
-      <c r="N248" s="29" t="str">
+      <c r="N248" s="28"/>
+      <c r="O248" s="29" t="str">
         <f aca="false">IF($M248="","",$M248*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O248" s="29" t="str">
-        <f aca="false">IF($M248="","",$M248*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P248" s="28"/>
@@ -15159,12 +14546,9 @@
       </c>
       <c r="L249" s="28"/>
       <c r="M249" s="27"/>
-      <c r="N249" s="29" t="str">
+      <c r="N249" s="28"/>
+      <c r="O249" s="29" t="str">
         <f aca="false">IF($M249="","",$M249*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O249" s="29" t="str">
-        <f aca="false">IF($M249="","",$M249*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P249" s="28"/>
@@ -15213,12 +14597,9 @@
       </c>
       <c r="L250" s="28"/>
       <c r="M250" s="27"/>
-      <c r="N250" s="29" t="str">
+      <c r="N250" s="28"/>
+      <c r="O250" s="29" t="str">
         <f aca="false">IF($M250="","",$M250*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O250" s="29" t="str">
-        <f aca="false">IF($M250="","",$M250*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P250" s="28"/>
@@ -15267,12 +14648,9 @@
       </c>
       <c r="L251" s="28"/>
       <c r="M251" s="27"/>
-      <c r="N251" s="29" t="str">
+      <c r="N251" s="28"/>
+      <c r="O251" s="29" t="str">
         <f aca="false">IF($M251="","",$M251*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O251" s="29" t="str">
-        <f aca="false">IF($M251="","",$M251*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P251" s="28"/>
@@ -15321,12 +14699,9 @@
       </c>
       <c r="L252" s="28"/>
       <c r="M252" s="27"/>
-      <c r="N252" s="29" t="str">
+      <c r="N252" s="28"/>
+      <c r="O252" s="29" t="str">
         <f aca="false">IF($M252="","",$M252*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O252" s="29" t="str">
-        <f aca="false">IF($M252="","",$M252*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P252" s="28"/>
@@ -15375,12 +14750,9 @@
       </c>
       <c r="L253" s="28"/>
       <c r="M253" s="27"/>
-      <c r="N253" s="29" t="str">
+      <c r="N253" s="28"/>
+      <c r="O253" s="29" t="str">
         <f aca="false">IF($M253="","",$M253*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O253" s="29" t="str">
-        <f aca="false">IF($M253="","",$M253*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P253" s="28"/>
@@ -15429,12 +14801,9 @@
       </c>
       <c r="L254" s="28"/>
       <c r="M254" s="27"/>
-      <c r="N254" s="29" t="str">
+      <c r="N254" s="28"/>
+      <c r="O254" s="29" t="str">
         <f aca="false">IF($M254="","",$M254*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O254" s="29" t="str">
-        <f aca="false">IF($M254="","",$M254*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P254" s="28"/>
@@ -15483,12 +14852,9 @@
       </c>
       <c r="L255" s="28"/>
       <c r="M255" s="27"/>
-      <c r="N255" s="29" t="str">
+      <c r="N255" s="28"/>
+      <c r="O255" s="29" t="str">
         <f aca="false">IF($M255="","",$M255*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O255" s="29" t="str">
-        <f aca="false">IF($M255="","",$M255*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P255" s="28"/>
@@ -15537,12 +14903,9 @@
       </c>
       <c r="L256" s="28"/>
       <c r="M256" s="27"/>
-      <c r="N256" s="29" t="str">
+      <c r="N256" s="28"/>
+      <c r="O256" s="29" t="str">
         <f aca="false">IF($M256="","",$M256*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O256" s="29" t="str">
-        <f aca="false">IF($M256="","",$M256*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P256" s="28"/>
@@ -15591,12 +14954,9 @@
       </c>
       <c r="L257" s="28"/>
       <c r="M257" s="27"/>
-      <c r="N257" s="29" t="str">
+      <c r="N257" s="28"/>
+      <c r="O257" s="29" t="str">
         <f aca="false">IF($M257="","",$M257*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O257" s="29" t="str">
-        <f aca="false">IF($M257="","",$M257*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P257" s="28"/>
@@ -15645,12 +15005,9 @@
       </c>
       <c r="L258" s="28"/>
       <c r="M258" s="27"/>
-      <c r="N258" s="29" t="str">
+      <c r="N258" s="28"/>
+      <c r="O258" s="29" t="str">
         <f aca="false">IF($M258="","",$M258*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O258" s="29" t="str">
-        <f aca="false">IF($M258="","",$M258*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P258" s="28"/>
@@ -15699,12 +15056,9 @@
       </c>
       <c r="L259" s="28"/>
       <c r="M259" s="27"/>
-      <c r="N259" s="29" t="str">
+      <c r="N259" s="28"/>
+      <c r="O259" s="29" t="str">
         <f aca="false">IF($M259="","",$M259*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O259" s="29" t="str">
-        <f aca="false">IF($M259="","",$M259*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P259" s="28"/>
@@ -15753,12 +15107,9 @@
       </c>
       <c r="L260" s="28"/>
       <c r="M260" s="27"/>
-      <c r="N260" s="29" t="str">
+      <c r="N260" s="28"/>
+      <c r="O260" s="29" t="str">
         <f aca="false">IF($M260="","",$M260*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O260" s="29" t="str">
-        <f aca="false">IF($M260="","",$M260*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P260" s="28"/>
@@ -15807,12 +15158,9 @@
       </c>
       <c r="L261" s="28"/>
       <c r="M261" s="27"/>
-      <c r="N261" s="29" t="str">
+      <c r="N261" s="28"/>
+      <c r="O261" s="29" t="str">
         <f aca="false">IF($M261="","",$M261*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O261" s="29" t="str">
-        <f aca="false">IF($M261="","",$M261*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P261" s="28"/>
@@ -15861,12 +15209,9 @@
       </c>
       <c r="L262" s="28"/>
       <c r="M262" s="27"/>
-      <c r="N262" s="29" t="str">
+      <c r="N262" s="28"/>
+      <c r="O262" s="29" t="str">
         <f aca="false">IF($M262="","",$M262*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O262" s="29" t="str">
-        <f aca="false">IF($M262="","",$M262*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P262" s="28"/>
@@ -15915,12 +15260,9 @@
       </c>
       <c r="L263" s="28"/>
       <c r="M263" s="27"/>
-      <c r="N263" s="29" t="str">
+      <c r="N263" s="28"/>
+      <c r="O263" s="29" t="str">
         <f aca="false">IF($M263="","",$M263*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O263" s="29" t="str">
-        <f aca="false">IF($M263="","",$M263*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P263" s="28"/>
@@ -15969,12 +15311,9 @@
       </c>
       <c r="L264" s="28"/>
       <c r="M264" s="27"/>
-      <c r="N264" s="29" t="str">
+      <c r="N264" s="28"/>
+      <c r="O264" s="29" t="str">
         <f aca="false">IF($M264="","",$M264*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O264" s="29" t="str">
-        <f aca="false">IF($M264="","",$M264*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P264" s="28"/>
@@ -16023,12 +15362,9 @@
       </c>
       <c r="L265" s="28"/>
       <c r="M265" s="27"/>
-      <c r="N265" s="29" t="str">
+      <c r="N265" s="28"/>
+      <c r="O265" s="29" t="str">
         <f aca="false">IF($M265="","",$M265*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O265" s="29" t="str">
-        <f aca="false">IF($M265="","",$M265*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P265" s="28"/>
@@ -16077,12 +15413,9 @@
       </c>
       <c r="L266" s="28"/>
       <c r="M266" s="27"/>
-      <c r="N266" s="29" t="str">
+      <c r="N266" s="28"/>
+      <c r="O266" s="29" t="str">
         <f aca="false">IF($M266="","",$M266*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O266" s="29" t="str">
-        <f aca="false">IF($M266="","",$M266*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P266" s="28"/>
@@ -16131,12 +15464,9 @@
       </c>
       <c r="L267" s="28"/>
       <c r="M267" s="27"/>
-      <c r="N267" s="29" t="str">
+      <c r="N267" s="28"/>
+      <c r="O267" s="29" t="str">
         <f aca="false">IF($M267="","",$M267*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O267" s="29" t="str">
-        <f aca="false">IF($M267="","",$M267*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P267" s="28"/>
@@ -16185,12 +15515,9 @@
       </c>
       <c r="L268" s="28"/>
       <c r="M268" s="27"/>
-      <c r="N268" s="29" t="str">
+      <c r="N268" s="28"/>
+      <c r="O268" s="29" t="str">
         <f aca="false">IF($M268="","",$M268*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O268" s="29" t="str">
-        <f aca="false">IF($M268="","",$M268*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P268" s="28"/>
@@ -16239,12 +15566,9 @@
       </c>
       <c r="L269" s="28"/>
       <c r="M269" s="27"/>
-      <c r="N269" s="29" t="str">
+      <c r="N269" s="28"/>
+      <c r="O269" s="29" t="str">
         <f aca="false">IF($M269="","",$M269*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O269" s="29" t="str">
-        <f aca="false">IF($M269="","",$M269*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P269" s="28"/>
@@ -16293,12 +15617,9 @@
       </c>
       <c r="L270" s="28"/>
       <c r="M270" s="27"/>
-      <c r="N270" s="29" t="str">
+      <c r="N270" s="28"/>
+      <c r="O270" s="29" t="str">
         <f aca="false">IF($M270="","",$M270*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O270" s="29" t="str">
-        <f aca="false">IF($M270="","",$M270*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P270" s="28"/>
@@ -16347,12 +15668,9 @@
       </c>
       <c r="L271" s="28"/>
       <c r="M271" s="27"/>
-      <c r="N271" s="29" t="str">
+      <c r="N271" s="28"/>
+      <c r="O271" s="29" t="str">
         <f aca="false">IF($M271="","",$M271*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O271" s="29" t="str">
-        <f aca="false">IF($M271="","",$M271*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P271" s="28"/>
@@ -16401,12 +15719,9 @@
       </c>
       <c r="L272" s="28"/>
       <c r="M272" s="27"/>
-      <c r="N272" s="29" t="str">
+      <c r="N272" s="28"/>
+      <c r="O272" s="29" t="str">
         <f aca="false">IF($M272="","",$M272*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O272" s="29" t="str">
-        <f aca="false">IF($M272="","",$M272*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P272" s="28"/>
@@ -16455,12 +15770,9 @@
       </c>
       <c r="L273" s="28"/>
       <c r="M273" s="27"/>
-      <c r="N273" s="29" t="str">
+      <c r="N273" s="28"/>
+      <c r="O273" s="29" t="str">
         <f aca="false">IF($M273="","",$M273*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O273" s="29" t="str">
-        <f aca="false">IF($M273="","",$M273*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P273" s="28"/>
@@ -16509,12 +15821,9 @@
       </c>
       <c r="L274" s="28"/>
       <c r="M274" s="27"/>
-      <c r="N274" s="29" t="str">
+      <c r="N274" s="28"/>
+      <c r="O274" s="29" t="str">
         <f aca="false">IF($M274="","",$M274*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O274" s="29" t="str">
-        <f aca="false">IF($M274="","",$M274*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P274" s="28"/>
@@ -16563,12 +15872,9 @@
       </c>
       <c r="L275" s="28"/>
       <c r="M275" s="27"/>
-      <c r="N275" s="29" t="str">
+      <c r="N275" s="28"/>
+      <c r="O275" s="29" t="str">
         <f aca="false">IF($M275="","",$M275*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O275" s="29" t="str">
-        <f aca="false">IF($M275="","",$M275*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P275" s="28"/>
@@ -16617,12 +15923,9 @@
       </c>
       <c r="L276" s="28"/>
       <c r="M276" s="27"/>
-      <c r="N276" s="29" t="str">
+      <c r="N276" s="28"/>
+      <c r="O276" s="29" t="str">
         <f aca="false">IF($M276="","",$M276*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O276" s="29" t="str">
-        <f aca="false">IF($M276="","",$M276*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P276" s="28"/>
@@ -16671,12 +15974,9 @@
       </c>
       <c r="L277" s="28"/>
       <c r="M277" s="27"/>
-      <c r="N277" s="29" t="str">
+      <c r="N277" s="28"/>
+      <c r="O277" s="29" t="str">
         <f aca="false">IF($M277="","",$M277*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O277" s="29" t="str">
-        <f aca="false">IF($M277="","",$M277*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P277" s="28"/>
@@ -16725,12 +16025,9 @@
       </c>
       <c r="L278" s="28"/>
       <c r="M278" s="27"/>
-      <c r="N278" s="29" t="str">
+      <c r="N278" s="28"/>
+      <c r="O278" s="29" t="str">
         <f aca="false">IF($M278="","",$M278*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O278" s="29" t="str">
-        <f aca="false">IF($M278="","",$M278*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P278" s="28"/>
@@ -16779,12 +16076,9 @@
       </c>
       <c r="L279" s="28"/>
       <c r="M279" s="27"/>
-      <c r="N279" s="29" t="str">
+      <c r="N279" s="28"/>
+      <c r="O279" s="29" t="str">
         <f aca="false">IF($M279="","",$M279*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O279" s="29" t="str">
-        <f aca="false">IF($M279="","",$M279*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P279" s="28"/>
@@ -16833,12 +16127,9 @@
       </c>
       <c r="L280" s="28"/>
       <c r="M280" s="27"/>
-      <c r="N280" s="29" t="str">
+      <c r="N280" s="28"/>
+      <c r="O280" s="29" t="str">
         <f aca="false">IF($M280="","",$M280*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O280" s="29" t="str">
-        <f aca="false">IF($M280="","",$M280*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P280" s="28"/>
@@ -16887,12 +16178,9 @@
       </c>
       <c r="L281" s="28"/>
       <c r="M281" s="27"/>
-      <c r="N281" s="29" t="str">
+      <c r="N281" s="28"/>
+      <c r="O281" s="29" t="str">
         <f aca="false">IF($M281="","",$M281*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O281" s="29" t="str">
-        <f aca="false">IF($M281="","",$M281*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P281" s="28"/>
@@ -16941,12 +16229,9 @@
       </c>
       <c r="L282" s="28"/>
       <c r="M282" s="27"/>
-      <c r="N282" s="29" t="str">
+      <c r="N282" s="28"/>
+      <c r="O282" s="29" t="str">
         <f aca="false">IF($M282="","",$M282*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O282" s="29" t="str">
-        <f aca="false">IF($M282="","",$M282*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P282" s="28"/>
@@ -16995,12 +16280,9 @@
       </c>
       <c r="L283" s="28"/>
       <c r="M283" s="27"/>
-      <c r="N283" s="29" t="str">
+      <c r="N283" s="28"/>
+      <c r="O283" s="29" t="str">
         <f aca="false">IF($M283="","",$M283*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O283" s="29" t="str">
-        <f aca="false">IF($M283="","",$M283*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P283" s="28"/>
@@ -17049,12 +16331,9 @@
       </c>
       <c r="L284" s="28"/>
       <c r="M284" s="27"/>
-      <c r="N284" s="29" t="str">
+      <c r="N284" s="28"/>
+      <c r="O284" s="29" t="str">
         <f aca="false">IF($M284="","",$M284*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O284" s="29" t="str">
-        <f aca="false">IF($M284="","",$M284*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P284" s="28"/>
@@ -17103,12 +16382,9 @@
       </c>
       <c r="L285" s="28"/>
       <c r="M285" s="27"/>
-      <c r="N285" s="29" t="str">
+      <c r="N285" s="28"/>
+      <c r="O285" s="29" t="str">
         <f aca="false">IF($M285="","",$M285*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O285" s="29" t="str">
-        <f aca="false">IF($M285="","",$M285*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P285" s="28"/>
@@ -17157,12 +16433,9 @@
       </c>
       <c r="L286" s="28"/>
       <c r="M286" s="27"/>
-      <c r="N286" s="29" t="str">
+      <c r="N286" s="28"/>
+      <c r="O286" s="29" t="str">
         <f aca="false">IF($M286="","",$M286*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O286" s="29" t="str">
-        <f aca="false">IF($M286="","",$M286*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P286" s="28"/>
@@ -17211,12 +16484,9 @@
       </c>
       <c r="L287" s="28"/>
       <c r="M287" s="27"/>
-      <c r="N287" s="29" t="str">
+      <c r="N287" s="28"/>
+      <c r="O287" s="29" t="str">
         <f aca="false">IF($M287="","",$M287*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O287" s="29" t="str">
-        <f aca="false">IF($M287="","",$M287*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P287" s="28"/>
@@ -17265,12 +16535,9 @@
       </c>
       <c r="L288" s="28"/>
       <c r="M288" s="27"/>
-      <c r="N288" s="29" t="str">
+      <c r="N288" s="28"/>
+      <c r="O288" s="29" t="str">
         <f aca="false">IF($M288="","",$M288*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O288" s="29" t="str">
-        <f aca="false">IF($M288="","",$M288*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P288" s="28"/>
@@ -17319,12 +16586,9 @@
       </c>
       <c r="L289" s="28"/>
       <c r="M289" s="27"/>
-      <c r="N289" s="29" t="str">
+      <c r="N289" s="28"/>
+      <c r="O289" s="29" t="str">
         <f aca="false">IF($M289="","",$M289*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O289" s="29" t="str">
-        <f aca="false">IF($M289="","",$M289*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P289" s="28"/>
@@ -17373,12 +16637,9 @@
       </c>
       <c r="L290" s="28"/>
       <c r="M290" s="27"/>
-      <c r="N290" s="29" t="str">
+      <c r="N290" s="28"/>
+      <c r="O290" s="29" t="str">
         <f aca="false">IF($M290="","",$M290*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O290" s="29" t="str">
-        <f aca="false">IF($M290="","",$M290*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P290" s="28"/>
@@ -17427,12 +16688,9 @@
       </c>
       <c r="L291" s="28"/>
       <c r="M291" s="27"/>
-      <c r="N291" s="29" t="str">
+      <c r="N291" s="28"/>
+      <c r="O291" s="29" t="str">
         <f aca="false">IF($M291="","",$M291*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O291" s="29" t="str">
-        <f aca="false">IF($M291="","",$M291*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P291" s="28"/>
@@ -17481,12 +16739,9 @@
       </c>
       <c r="L292" s="28"/>
       <c r="M292" s="27"/>
-      <c r="N292" s="29" t="str">
+      <c r="N292" s="28"/>
+      <c r="O292" s="29" t="str">
         <f aca="false">IF($M292="","",$M292*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O292" s="29" t="str">
-        <f aca="false">IF($M292="","",$M292*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P292" s="28"/>
@@ -17535,12 +16790,9 @@
       </c>
       <c r="L293" s="28"/>
       <c r="M293" s="27"/>
-      <c r="N293" s="29" t="str">
+      <c r="N293" s="28"/>
+      <c r="O293" s="29" t="str">
         <f aca="false">IF($M293="","",$M293*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O293" s="29" t="str">
-        <f aca="false">IF($M293="","",$M293*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P293" s="28"/>
@@ -17589,12 +16841,9 @@
       </c>
       <c r="L294" s="28"/>
       <c r="M294" s="27"/>
-      <c r="N294" s="29" t="str">
+      <c r="N294" s="28"/>
+      <c r="O294" s="29" t="str">
         <f aca="false">IF($M294="","",$M294*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O294" s="29" t="str">
-        <f aca="false">IF($M294="","",$M294*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P294" s="28"/>
@@ -17643,12 +16892,9 @@
       </c>
       <c r="L295" s="28"/>
       <c r="M295" s="27"/>
-      <c r="N295" s="29" t="str">
+      <c r="N295" s="28"/>
+      <c r="O295" s="29" t="str">
         <f aca="false">IF($M295="","",$M295*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O295" s="29" t="str">
-        <f aca="false">IF($M295="","",$M295*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P295" s="28"/>
@@ -17697,12 +16943,9 @@
       </c>
       <c r="L296" s="28"/>
       <c r="M296" s="27"/>
-      <c r="N296" s="29" t="str">
+      <c r="N296" s="28"/>
+      <c r="O296" s="29" t="str">
         <f aca="false">IF($M296="","",$M296*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O296" s="29" t="str">
-        <f aca="false">IF($M296="","",$M296*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P296" s="28"/>
@@ -17751,12 +16994,9 @@
       </c>
       <c r="L297" s="28"/>
       <c r="M297" s="27"/>
-      <c r="N297" s="29" t="str">
+      <c r="N297" s="28"/>
+      <c r="O297" s="29" t="str">
         <f aca="false">IF($M297="","",$M297*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O297" s="29" t="str">
-        <f aca="false">IF($M297="","",$M297*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P297" s="28"/>
@@ -17805,12 +17045,9 @@
       </c>
       <c r="L298" s="28"/>
       <c r="M298" s="27"/>
-      <c r="N298" s="29" t="str">
+      <c r="N298" s="28"/>
+      <c r="O298" s="29" t="str">
         <f aca="false">IF($M298="","",$M298*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O298" s="29" t="str">
-        <f aca="false">IF($M298="","",$M298*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P298" s="28"/>
@@ -17859,12 +17096,9 @@
       </c>
       <c r="L299" s="28"/>
       <c r="M299" s="27"/>
-      <c r="N299" s="29" t="str">
+      <c r="N299" s="28"/>
+      <c r="O299" s="29" t="str">
         <f aca="false">IF($M299="","",$M299*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O299" s="29" t="str">
-        <f aca="false">IF($M299="","",$M299*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P299" s="28"/>
@@ -17913,12 +17147,9 @@
       </c>
       <c r="L300" s="28"/>
       <c r="M300" s="27"/>
-      <c r="N300" s="29" t="str">
+      <c r="N300" s="28"/>
+      <c r="O300" s="29" t="str">
         <f aca="false">IF($M300="","",$M300*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O300" s="29" t="str">
-        <f aca="false">IF($M300="","",$M300*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P300" s="28"/>
@@ -17967,12 +17198,9 @@
       </c>
       <c r="L301" s="28"/>
       <c r="M301" s="27"/>
-      <c r="N301" s="29" t="str">
+      <c r="N301" s="28"/>
+      <c r="O301" s="29" t="str">
         <f aca="false">IF($M301="","",$M301*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O301" s="29" t="str">
-        <f aca="false">IF($M301="","",$M301*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P301" s="28"/>
@@ -18021,12 +17249,9 @@
       </c>
       <c r="L302" s="28"/>
       <c r="M302" s="27"/>
-      <c r="N302" s="29" t="str">
+      <c r="N302" s="28"/>
+      <c r="O302" s="29" t="str">
         <f aca="false">IF($M302="","",$M302*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O302" s="29" t="str">
-        <f aca="false">IF($M302="","",$M302*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P302" s="28"/>
@@ -18075,12 +17300,9 @@
       </c>
       <c r="L303" s="28"/>
       <c r="M303" s="27"/>
-      <c r="N303" s="29" t="str">
+      <c r="N303" s="28"/>
+      <c r="O303" s="29" t="str">
         <f aca="false">IF($M303="","",$M303*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O303" s="29" t="str">
-        <f aca="false">IF($M303="","",$M303*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P303" s="28"/>
@@ -18129,12 +17351,9 @@
       </c>
       <c r="L304" s="28"/>
       <c r="M304" s="27"/>
-      <c r="N304" s="29" t="str">
+      <c r="N304" s="28"/>
+      <c r="O304" s="29" t="str">
         <f aca="false">IF($M304="","",$M304*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O304" s="29" t="str">
-        <f aca="false">IF($M304="","",$M304*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P304" s="28"/>
@@ -18183,12 +17402,9 @@
       </c>
       <c r="L305" s="28"/>
       <c r="M305" s="27"/>
-      <c r="N305" s="29" t="str">
+      <c r="N305" s="28"/>
+      <c r="O305" s="29" t="str">
         <f aca="false">IF($M305="","",$M305*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O305" s="29" t="str">
-        <f aca="false">IF($M305="","",$M305*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P305" s="28"/>
@@ -18237,12 +17453,9 @@
       </c>
       <c r="L306" s="28"/>
       <c r="M306" s="27"/>
-      <c r="N306" s="29" t="str">
+      <c r="N306" s="28"/>
+      <c r="O306" s="29" t="str">
         <f aca="false">IF($M306="","",$M306*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O306" s="29" t="str">
-        <f aca="false">IF($M306="","",$M306*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P306" s="28"/>
@@ -18291,12 +17504,9 @@
       </c>
       <c r="L307" s="28"/>
       <c r="M307" s="27"/>
-      <c r="N307" s="29" t="str">
+      <c r="N307" s="28"/>
+      <c r="O307" s="29" t="str">
         <f aca="false">IF($M307="","",$M307*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O307" s="29" t="str">
-        <f aca="false">IF($M307="","",$M307*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P307" s="28"/>
@@ -18345,12 +17555,9 @@
       </c>
       <c r="L308" s="28"/>
       <c r="M308" s="27"/>
-      <c r="N308" s="29" t="str">
+      <c r="N308" s="28"/>
+      <c r="O308" s="29" t="str">
         <f aca="false">IF($M308="","",$M308*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O308" s="29" t="str">
-        <f aca="false">IF($M308="","",$M308*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P308" s="28"/>
@@ -18399,12 +17606,9 @@
       </c>
       <c r="L309" s="28"/>
       <c r="M309" s="27"/>
-      <c r="N309" s="29" t="str">
+      <c r="N309" s="28"/>
+      <c r="O309" s="29" t="str">
         <f aca="false">IF($M309="","",$M309*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O309" s="29" t="str">
-        <f aca="false">IF($M309="","",$M309*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P309" s="28"/>
@@ -18453,12 +17657,9 @@
       </c>
       <c r="L310" s="28"/>
       <c r="M310" s="27"/>
-      <c r="N310" s="29" t="str">
+      <c r="N310" s="28"/>
+      <c r="O310" s="29" t="str">
         <f aca="false">IF($M310="","",$M310*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O310" s="29" t="str">
-        <f aca="false">IF($M310="","",$M310*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P310" s="28"/>
@@ -18507,12 +17708,9 @@
       </c>
       <c r="L311" s="28"/>
       <c r="M311" s="27"/>
-      <c r="N311" s="29" t="str">
+      <c r="N311" s="28"/>
+      <c r="O311" s="29" t="str">
         <f aca="false">IF($M311="","",$M311*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O311" s="29" t="str">
-        <f aca="false">IF($M311="","",$M311*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P311" s="28"/>
@@ -18561,12 +17759,9 @@
       </c>
       <c r="L312" s="28"/>
       <c r="M312" s="27"/>
-      <c r="N312" s="29" t="str">
+      <c r="N312" s="28"/>
+      <c r="O312" s="29" t="str">
         <f aca="false">IF($M312="","",$M312*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O312" s="29" t="str">
-        <f aca="false">IF($M312="","",$M312*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P312" s="28"/>
@@ -18615,12 +17810,9 @@
       </c>
       <c r="L313" s="28"/>
       <c r="M313" s="27"/>
-      <c r="N313" s="29" t="str">
+      <c r="N313" s="28"/>
+      <c r="O313" s="29" t="str">
         <f aca="false">IF($M313="","",$M313*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O313" s="29" t="str">
-        <f aca="false">IF($M313="","",$M313*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P313" s="28"/>
@@ -18669,12 +17861,9 @@
       </c>
       <c r="L314" s="28"/>
       <c r="M314" s="27"/>
-      <c r="N314" s="29" t="str">
+      <c r="N314" s="28"/>
+      <c r="O314" s="29" t="str">
         <f aca="false">IF($M314="","",$M314*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O314" s="29" t="str">
-        <f aca="false">IF($M314="","",$M314*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P314" s="28"/>
@@ -18723,12 +17912,9 @@
       </c>
       <c r="L315" s="28"/>
       <c r="M315" s="27"/>
-      <c r="N315" s="29" t="str">
+      <c r="N315" s="28"/>
+      <c r="O315" s="29" t="str">
         <f aca="false">IF($M315="","",$M315*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O315" s="29" t="str">
-        <f aca="false">IF($M315="","",$M315*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P315" s="28"/>
@@ -18777,12 +17963,9 @@
       </c>
       <c r="L316" s="28"/>
       <c r="M316" s="27"/>
-      <c r="N316" s="29" t="str">
+      <c r="N316" s="28"/>
+      <c r="O316" s="29" t="str">
         <f aca="false">IF($M316="","",$M316*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O316" s="29" t="str">
-        <f aca="false">IF($M316="","",$M316*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P316" s="28"/>
@@ -18831,12 +18014,9 @@
       </c>
       <c r="L317" s="28"/>
       <c r="M317" s="27"/>
-      <c r="N317" s="29" t="str">
+      <c r="N317" s="28"/>
+      <c r="O317" s="29" t="str">
         <f aca="false">IF($M317="","",$M317*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O317" s="29" t="str">
-        <f aca="false">IF($M317="","",$M317*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P317" s="28"/>
@@ -18885,12 +18065,9 @@
       </c>
       <c r="L318" s="28"/>
       <c r="M318" s="27"/>
-      <c r="N318" s="29" t="str">
+      <c r="N318" s="28"/>
+      <c r="O318" s="29" t="str">
         <f aca="false">IF($M318="","",$M318*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O318" s="29" t="str">
-        <f aca="false">IF($M318="","",$M318*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P318" s="28"/>
@@ -18939,12 +18116,9 @@
       </c>
       <c r="L319" s="28"/>
       <c r="M319" s="27"/>
-      <c r="N319" s="29" t="str">
+      <c r="N319" s="28"/>
+      <c r="O319" s="29" t="str">
         <f aca="false">IF($M319="","",$M319*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O319" s="29" t="str">
-        <f aca="false">IF($M319="","",$M319*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P319" s="28"/>
@@ -18993,12 +18167,9 @@
       </c>
       <c r="L320" s="28"/>
       <c r="M320" s="27"/>
-      <c r="N320" s="29" t="str">
+      <c r="N320" s="28"/>
+      <c r="O320" s="29" t="str">
         <f aca="false">IF($M320="","",$M320*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O320" s="29" t="str">
-        <f aca="false">IF($M320="","",$M320*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P320" s="28"/>
@@ -19047,12 +18218,9 @@
       </c>
       <c r="L321" s="28"/>
       <c r="M321" s="27"/>
-      <c r="N321" s="29" t="str">
+      <c r="N321" s="28"/>
+      <c r="O321" s="29" t="str">
         <f aca="false">IF($M321="","",$M321*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O321" s="29" t="str">
-        <f aca="false">IF($M321="","",$M321*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P321" s="28"/>
@@ -19101,12 +18269,9 @@
       </c>
       <c r="L322" s="28"/>
       <c r="M322" s="27"/>
-      <c r="N322" s="29" t="str">
+      <c r="N322" s="28"/>
+      <c r="O322" s="29" t="str">
         <f aca="false">IF($M322="","",$M322*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O322" s="29" t="str">
-        <f aca="false">IF($M322="","",$M322*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P322" s="28"/>
@@ -19155,12 +18320,9 @@
       </c>
       <c r="L323" s="28"/>
       <c r="M323" s="27"/>
-      <c r="N323" s="29" t="str">
+      <c r="N323" s="28"/>
+      <c r="O323" s="29" t="str">
         <f aca="false">IF($M323="","",$M323*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O323" s="29" t="str">
-        <f aca="false">IF($M323="","",$M323*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P323" s="28"/>
@@ -19209,12 +18371,9 @@
       </c>
       <c r="L324" s="28"/>
       <c r="M324" s="27"/>
-      <c r="N324" s="29" t="str">
+      <c r="N324" s="28"/>
+      <c r="O324" s="29" t="str">
         <f aca="false">IF($M324="","",$M324*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O324" s="29" t="str">
-        <f aca="false">IF($M324="","",$M324*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P324" s="28"/>
@@ -19263,12 +18422,9 @@
       </c>
       <c r="L325" s="28"/>
       <c r="M325" s="27"/>
-      <c r="N325" s="29" t="str">
+      <c r="N325" s="28"/>
+      <c r="O325" s="29" t="str">
         <f aca="false">IF($M325="","",$M325*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O325" s="29" t="str">
-        <f aca="false">IF($M325="","",$M325*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P325" s="28"/>
@@ -19317,12 +18473,9 @@
       </c>
       <c r="L326" s="28"/>
       <c r="M326" s="27"/>
-      <c r="N326" s="29" t="str">
+      <c r="N326" s="28"/>
+      <c r="O326" s="29" t="str">
         <f aca="false">IF($M326="","",$M326*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O326" s="29" t="str">
-        <f aca="false">IF($M326="","",$M326*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P326" s="28"/>
@@ -19371,12 +18524,9 @@
       </c>
       <c r="L327" s="28"/>
       <c r="M327" s="27"/>
-      <c r="N327" s="29" t="str">
+      <c r="N327" s="28"/>
+      <c r="O327" s="29" t="str">
         <f aca="false">IF($M327="","",$M327*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O327" s="29" t="str">
-        <f aca="false">IF($M327="","",$M327*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P327" s="28"/>
@@ -19425,12 +18575,9 @@
       </c>
       <c r="L328" s="28"/>
       <c r="M328" s="27"/>
-      <c r="N328" s="29" t="str">
+      <c r="N328" s="28"/>
+      <c r="O328" s="29" t="str">
         <f aca="false">IF($M328="","",$M328*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O328" s="29" t="str">
-        <f aca="false">IF($M328="","",$M328*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P328" s="28"/>
@@ -19479,12 +18626,9 @@
       </c>
       <c r="L329" s="28"/>
       <c r="M329" s="27"/>
-      <c r="N329" s="29" t="str">
+      <c r="N329" s="28"/>
+      <c r="O329" s="29" t="str">
         <f aca="false">IF($M329="","",$M329*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O329" s="29" t="str">
-        <f aca="false">IF($M329="","",$M329*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P329" s="28"/>
@@ -19533,12 +18677,9 @@
       </c>
       <c r="L330" s="28"/>
       <c r="M330" s="27"/>
-      <c r="N330" s="29" t="str">
+      <c r="N330" s="28"/>
+      <c r="O330" s="29" t="str">
         <f aca="false">IF($M330="","",$M330*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O330" s="29" t="str">
-        <f aca="false">IF($M330="","",$M330*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P330" s="28"/>
@@ -19587,12 +18728,9 @@
       </c>
       <c r="L331" s="28"/>
       <c r="M331" s="27"/>
-      <c r="N331" s="29" t="str">
+      <c r="N331" s="28"/>
+      <c r="O331" s="29" t="str">
         <f aca="false">IF($M331="","",$M331*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O331" s="29" t="str">
-        <f aca="false">IF($M331="","",$M331*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P331" s="28"/>
@@ -19641,12 +18779,9 @@
       </c>
       <c r="L332" s="28"/>
       <c r="M332" s="27"/>
-      <c r="N332" s="29" t="str">
+      <c r="N332" s="28"/>
+      <c r="O332" s="29" t="str">
         <f aca="false">IF($M332="","",$M332*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O332" s="29" t="str">
-        <f aca="false">IF($M332="","",$M332*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P332" s="28"/>
@@ -19695,12 +18830,9 @@
       </c>
       <c r="L333" s="28"/>
       <c r="M333" s="27"/>
-      <c r="N333" s="29" t="str">
+      <c r="N333" s="28"/>
+      <c r="O333" s="29" t="str">
         <f aca="false">IF($M333="","",$M333*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O333" s="29" t="str">
-        <f aca="false">IF($M333="","",$M333*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P333" s="28"/>
@@ -19749,12 +18881,9 @@
       </c>
       <c r="L334" s="28"/>
       <c r="M334" s="27"/>
-      <c r="N334" s="29" t="str">
+      <c r="N334" s="28"/>
+      <c r="O334" s="29" t="str">
         <f aca="false">IF($M334="","",$M334*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O334" s="29" t="str">
-        <f aca="false">IF($M334="","",$M334*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P334" s="28"/>
@@ -19803,12 +18932,9 @@
       </c>
       <c r="L335" s="28"/>
       <c r="M335" s="27"/>
-      <c r="N335" s="29" t="str">
+      <c r="N335" s="28"/>
+      <c r="O335" s="29" t="str">
         <f aca="false">IF($M335="","",$M335*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O335" s="29" t="str">
-        <f aca="false">IF($M335="","",$M335*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P335" s="28"/>
@@ -19857,12 +18983,9 @@
       </c>
       <c r="L336" s="28"/>
       <c r="M336" s="27"/>
-      <c r="N336" s="29" t="str">
+      <c r="N336" s="28"/>
+      <c r="O336" s="29" t="str">
         <f aca="false">IF($M336="","",$M336*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O336" s="29" t="str">
-        <f aca="false">IF($M336="","",$M336*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P336" s="28"/>
@@ -19911,12 +19034,9 @@
       </c>
       <c r="L337" s="28"/>
       <c r="M337" s="27"/>
-      <c r="N337" s="29" t="str">
+      <c r="N337" s="28"/>
+      <c r="O337" s="29" t="str">
         <f aca="false">IF($M337="","",$M337*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O337" s="29" t="str">
-        <f aca="false">IF($M337="","",$M337*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P337" s="28"/>
@@ -19965,12 +19085,9 @@
       </c>
       <c r="L338" s="28"/>
       <c r="M338" s="27"/>
-      <c r="N338" s="29" t="str">
+      <c r="N338" s="28"/>
+      <c r="O338" s="29" t="str">
         <f aca="false">IF($M338="","",$M338*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O338" s="29" t="str">
-        <f aca="false">IF($M338="","",$M338*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P338" s="28"/>
@@ -20019,12 +19136,9 @@
       </c>
       <c r="L339" s="28"/>
       <c r="M339" s="27"/>
-      <c r="N339" s="29" t="str">
+      <c r="N339" s="28"/>
+      <c r="O339" s="29" t="str">
         <f aca="false">IF($M339="","",$M339*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O339" s="29" t="str">
-        <f aca="false">IF($M339="","",$M339*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P339" s="28"/>
@@ -20073,12 +19187,9 @@
       </c>
       <c r="L340" s="28"/>
       <c r="M340" s="27"/>
-      <c r="N340" s="29" t="str">
+      <c r="N340" s="28"/>
+      <c r="O340" s="29" t="str">
         <f aca="false">IF($M340="","",$M340*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O340" s="29" t="str">
-        <f aca="false">IF($M340="","",$M340*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P340" s="28"/>
@@ -20127,12 +19238,9 @@
       </c>
       <c r="L341" s="28"/>
       <c r="M341" s="27"/>
-      <c r="N341" s="29" t="str">
+      <c r="N341" s="28"/>
+      <c r="O341" s="29" t="str">
         <f aca="false">IF($M341="","",$M341*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O341" s="29" t="str">
-        <f aca="false">IF($M341="","",$M341*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P341" s="28"/>
@@ -20181,12 +19289,9 @@
       </c>
       <c r="L342" s="28"/>
       <c r="M342" s="27"/>
-      <c r="N342" s="29" t="str">
+      <c r="N342" s="28"/>
+      <c r="O342" s="29" t="str">
         <f aca="false">IF($M342="","",$M342*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O342" s="29" t="str">
-        <f aca="false">IF($M342="","",$M342*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P342" s="28"/>
@@ -20235,12 +19340,9 @@
       </c>
       <c r="L343" s="28"/>
       <c r="M343" s="27"/>
-      <c r="N343" s="29" t="str">
+      <c r="N343" s="28"/>
+      <c r="O343" s="29" t="str">
         <f aca="false">IF($M343="","",$M343*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O343" s="29" t="str">
-        <f aca="false">IF($M343="","",$M343*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P343" s="28"/>
@@ -20289,12 +19391,9 @@
       </c>
       <c r="L344" s="28"/>
       <c r="M344" s="27"/>
-      <c r="N344" s="29" t="str">
+      <c r="N344" s="28"/>
+      <c r="O344" s="29" t="str">
         <f aca="false">IF($M344="","",$M344*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O344" s="29" t="str">
-        <f aca="false">IF($M344="","",$M344*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P344" s="28"/>
@@ -20343,12 +19442,9 @@
       </c>
       <c r="L345" s="28"/>
       <c r="M345" s="27"/>
-      <c r="N345" s="29" t="str">
+      <c r="N345" s="28"/>
+      <c r="O345" s="29" t="str">
         <f aca="false">IF($M345="","",$M345*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O345" s="29" t="str">
-        <f aca="false">IF($M345="","",$M345*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P345" s="28"/>
@@ -20397,12 +19493,9 @@
       </c>
       <c r="L346" s="28"/>
       <c r="M346" s="27"/>
-      <c r="N346" s="29" t="str">
+      <c r="N346" s="28"/>
+      <c r="O346" s="29" t="str">
         <f aca="false">IF($M346="","",$M346*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O346" s="29" t="str">
-        <f aca="false">IF($M346="","",$M346*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P346" s="28"/>
@@ -20451,12 +19544,9 @@
       </c>
       <c r="L347" s="28"/>
       <c r="M347" s="27"/>
-      <c r="N347" s="29" t="str">
+      <c r="N347" s="28"/>
+      <c r="O347" s="29" t="str">
         <f aca="false">IF($M347="","",$M347*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O347" s="29" t="str">
-        <f aca="false">IF($M347="","",$M347*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P347" s="28"/>
@@ -20505,12 +19595,9 @@
       </c>
       <c r="L348" s="28"/>
       <c r="M348" s="27"/>
-      <c r="N348" s="29" t="str">
+      <c r="N348" s="28"/>
+      <c r="O348" s="29" t="str">
         <f aca="false">IF($M348="","",$M348*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O348" s="29" t="str">
-        <f aca="false">IF($M348="","",$M348*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P348" s="28"/>
@@ -20559,12 +19646,9 @@
       </c>
       <c r="L349" s="28"/>
       <c r="M349" s="27"/>
-      <c r="N349" s="29" t="str">
+      <c r="N349" s="28"/>
+      <c r="O349" s="29" t="str">
         <f aca="false">IF($M349="","",$M349*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O349" s="29" t="str">
-        <f aca="false">IF($M349="","",$M349*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P349" s="28"/>
@@ -20613,12 +19697,9 @@
       </c>
       <c r="L350" s="28"/>
       <c r="M350" s="27"/>
-      <c r="N350" s="29" t="str">
+      <c r="N350" s="28"/>
+      <c r="O350" s="29" t="str">
         <f aca="false">IF($M350="","",$M350*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O350" s="29" t="str">
-        <f aca="false">IF($M350="","",$M350*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P350" s="28"/>
@@ -20667,12 +19748,9 @@
       </c>
       <c r="L351" s="28"/>
       <c r="M351" s="27"/>
-      <c r="N351" s="29" t="str">
+      <c r="N351" s="28"/>
+      <c r="O351" s="29" t="str">
         <f aca="false">IF($M351="","",$M351*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O351" s="29" t="str">
-        <f aca="false">IF($M351="","",$M351*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P351" s="28"/>
@@ -20721,12 +19799,9 @@
       </c>
       <c r="L352" s="28"/>
       <c r="M352" s="27"/>
-      <c r="N352" s="29" t="str">
+      <c r="N352" s="28"/>
+      <c r="O352" s="29" t="str">
         <f aca="false">IF($M352="","",$M352*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O352" s="29" t="str">
-        <f aca="false">IF($M352="","",$M352*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P352" s="28"/>
@@ -20775,12 +19850,9 @@
       </c>
       <c r="L353" s="28"/>
       <c r="M353" s="27"/>
-      <c r="N353" s="29" t="str">
+      <c r="N353" s="28"/>
+      <c r="O353" s="29" t="str">
         <f aca="false">IF($M353="","",$M353*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O353" s="29" t="str">
-        <f aca="false">IF($M353="","",$M353*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P353" s="28"/>
@@ -20829,12 +19901,9 @@
       </c>
       <c r="L354" s="28"/>
       <c r="M354" s="27"/>
-      <c r="N354" s="29" t="str">
+      <c r="N354" s="28"/>
+      <c r="O354" s="29" t="str">
         <f aca="false">IF($M354="","",$M354*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O354" s="29" t="str">
-        <f aca="false">IF($M354="","",$M354*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P354" s="28"/>
@@ -20883,12 +19952,9 @@
       </c>
       <c r="L355" s="28"/>
       <c r="M355" s="27"/>
-      <c r="N355" s="29" t="str">
+      <c r="N355" s="28"/>
+      <c r="O355" s="29" t="str">
         <f aca="false">IF($M355="","",$M355*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O355" s="29" t="str">
-        <f aca="false">IF($M355="","",$M355*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P355" s="28"/>
@@ -20937,12 +20003,9 @@
       </c>
       <c r="L356" s="28"/>
       <c r="M356" s="27"/>
-      <c r="N356" s="29" t="str">
+      <c r="N356" s="28"/>
+      <c r="O356" s="29" t="str">
         <f aca="false">IF($M356="","",$M356*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O356" s="29" t="str">
-        <f aca="false">IF($M356="","",$M356*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P356" s="28"/>
@@ -20991,12 +20054,9 @@
       </c>
       <c r="L357" s="28"/>
       <c r="M357" s="27"/>
-      <c r="N357" s="29" t="str">
+      <c r="N357" s="28"/>
+      <c r="O357" s="29" t="str">
         <f aca="false">IF($M357="","",$M357*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O357" s="29" t="str">
-        <f aca="false">IF($M357="","",$M357*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P357" s="28"/>
@@ -21045,12 +20105,9 @@
       </c>
       <c r="L358" s="28"/>
       <c r="M358" s="27"/>
-      <c r="N358" s="29" t="str">
+      <c r="N358" s="28"/>
+      <c r="O358" s="29" t="str">
         <f aca="false">IF($M358="","",$M358*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O358" s="29" t="str">
-        <f aca="false">IF($M358="","",$M358*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P358" s="28"/>
@@ -21099,12 +20156,9 @@
       </c>
       <c r="L359" s="28"/>
       <c r="M359" s="27"/>
-      <c r="N359" s="29" t="str">
+      <c r="N359" s="28"/>
+      <c r="O359" s="29" t="str">
         <f aca="false">IF($M359="","",$M359*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O359" s="29" t="str">
-        <f aca="false">IF($M359="","",$M359*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P359" s="28"/>
@@ -21153,12 +20207,9 @@
       </c>
       <c r="L360" s="28"/>
       <c r="M360" s="27"/>
-      <c r="N360" s="29" t="str">
+      <c r="N360" s="28"/>
+      <c r="O360" s="29" t="str">
         <f aca="false">IF($M360="","",$M360*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O360" s="29" t="str">
-        <f aca="false">IF($M360="","",$M360*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P360" s="28"/>
@@ -21207,12 +20258,9 @@
       </c>
       <c r="L361" s="28"/>
       <c r="M361" s="27"/>
-      <c r="N361" s="29" t="str">
+      <c r="N361" s="28"/>
+      <c r="O361" s="29" t="str">
         <f aca="false">IF($M361="","",$M361*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O361" s="29" t="str">
-        <f aca="false">IF($M361="","",$M361*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P361" s="28"/>
@@ -21261,12 +20309,9 @@
       </c>
       <c r="L362" s="28"/>
       <c r="M362" s="27"/>
-      <c r="N362" s="29" t="str">
+      <c r="N362" s="28"/>
+      <c r="O362" s="29" t="str">
         <f aca="false">IF($M362="","",$M362*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O362" s="29" t="str">
-        <f aca="false">IF($M362="","",$M362*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P362" s="28"/>
@@ -21315,12 +20360,9 @@
       </c>
       <c r="L363" s="28"/>
       <c r="M363" s="27"/>
-      <c r="N363" s="29" t="str">
+      <c r="N363" s="28"/>
+      <c r="O363" s="29" t="str">
         <f aca="false">IF($M363="","",$M363*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O363" s="29" t="str">
-        <f aca="false">IF($M363="","",$M363*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P363" s="28"/>
@@ -21369,12 +20411,9 @@
       </c>
       <c r="L364" s="28"/>
       <c r="M364" s="27"/>
-      <c r="N364" s="29" t="str">
+      <c r="N364" s="28"/>
+      <c r="O364" s="29" t="str">
         <f aca="false">IF($M364="","",$M364*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O364" s="29" t="str">
-        <f aca="false">IF($M364="","",$M364*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P364" s="28"/>
@@ -21423,12 +20462,9 @@
       </c>
       <c r="L365" s="28"/>
       <c r="M365" s="27"/>
-      <c r="N365" s="29" t="str">
+      <c r="N365" s="28"/>
+      <c r="O365" s="29" t="str">
         <f aca="false">IF($M365="","",$M365*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O365" s="29" t="str">
-        <f aca="false">IF($M365="","",$M365*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P365" s="28"/>
@@ -21477,12 +20513,9 @@
       </c>
       <c r="L366" s="28"/>
       <c r="M366" s="27"/>
-      <c r="N366" s="29" t="str">
+      <c r="N366" s="28"/>
+      <c r="O366" s="29" t="str">
         <f aca="false">IF($M366="","",$M366*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O366" s="29" t="str">
-        <f aca="false">IF($M366="","",$M366*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P366" s="28"/>
@@ -21531,12 +20564,9 @@
       </c>
       <c r="L367" s="28"/>
       <c r="M367" s="27"/>
-      <c r="N367" s="29" t="str">
+      <c r="N367" s="28"/>
+      <c r="O367" s="29" t="str">
         <f aca="false">IF($M367="","",$M367*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O367" s="29" t="str">
-        <f aca="false">IF($M367="","",$M367*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P367" s="28"/>
@@ -21585,12 +20615,9 @@
       </c>
       <c r="L368" s="28"/>
       <c r="M368" s="27"/>
-      <c r="N368" s="29" t="str">
+      <c r="N368" s="28"/>
+      <c r="O368" s="29" t="str">
         <f aca="false">IF($M368="","",$M368*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O368" s="29" t="str">
-        <f aca="false">IF($M368="","",$M368*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P368" s="28"/>
@@ -21639,12 +20666,9 @@
       </c>
       <c r="L369" s="28"/>
       <c r="M369" s="27"/>
-      <c r="N369" s="29" t="str">
+      <c r="N369" s="28"/>
+      <c r="O369" s="29" t="str">
         <f aca="false">IF($M369="","",$M369*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O369" s="29" t="str">
-        <f aca="false">IF($M369="","",$M369*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P369" s="28"/>
@@ -21693,12 +20717,9 @@
       </c>
       <c r="L370" s="28"/>
       <c r="M370" s="27"/>
-      <c r="N370" s="29" t="str">
+      <c r="N370" s="28"/>
+      <c r="O370" s="29" t="str">
         <f aca="false">IF($M370="","",$M370*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O370" s="29" t="str">
-        <f aca="false">IF($M370="","",$M370*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P370" s="28"/>
@@ -21747,12 +20768,9 @@
       </c>
       <c r="L371" s="28"/>
       <c r="M371" s="27"/>
-      <c r="N371" s="29" t="str">
+      <c r="N371" s="28"/>
+      <c r="O371" s="29" t="str">
         <f aca="false">IF($M371="","",$M371*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O371" s="29" t="str">
-        <f aca="false">IF($M371="","",$M371*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P371" s="28"/>
@@ -21801,12 +20819,9 @@
       </c>
       <c r="L372" s="28"/>
       <c r="M372" s="27"/>
-      <c r="N372" s="29" t="str">
+      <c r="N372" s="28"/>
+      <c r="O372" s="29" t="str">
         <f aca="false">IF($M372="","",$M372*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O372" s="29" t="str">
-        <f aca="false">IF($M372="","",$M372*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P372" s="28"/>
@@ -21855,12 +20870,9 @@
       </c>
       <c r="L373" s="28"/>
       <c r="M373" s="27"/>
-      <c r="N373" s="29" t="str">
+      <c r="N373" s="28"/>
+      <c r="O373" s="29" t="str">
         <f aca="false">IF($M373="","",$M373*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O373" s="29" t="str">
-        <f aca="false">IF($M373="","",$M373*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P373" s="28"/>
@@ -21909,12 +20921,9 @@
       </c>
       <c r="L374" s="28"/>
       <c r="M374" s="27"/>
-      <c r="N374" s="29" t="str">
+      <c r="N374" s="28"/>
+      <c r="O374" s="29" t="str">
         <f aca="false">IF($M374="","",$M374*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O374" s="29" t="str">
-        <f aca="false">IF($M374="","",$M374*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P374" s="28"/>
@@ -21963,12 +20972,9 @@
       </c>
       <c r="L375" s="28"/>
       <c r="M375" s="27"/>
-      <c r="N375" s="29" t="str">
+      <c r="N375" s="28"/>
+      <c r="O375" s="29" t="str">
         <f aca="false">IF($M375="","",$M375*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O375" s="29" t="str">
-        <f aca="false">IF($M375="","",$M375*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P375" s="28"/>
@@ -22017,12 +21023,9 @@
       </c>
       <c r="L376" s="28"/>
       <c r="M376" s="27"/>
-      <c r="N376" s="29" t="str">
+      <c r="N376" s="28"/>
+      <c r="O376" s="29" t="str">
         <f aca="false">IF($M376="","",$M376*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O376" s="29" t="str">
-        <f aca="false">IF($M376="","",$M376*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P376" s="28"/>
@@ -22071,12 +21074,9 @@
       </c>
       <c r="L377" s="28"/>
       <c r="M377" s="27"/>
-      <c r="N377" s="29" t="str">
+      <c r="N377" s="28"/>
+      <c r="O377" s="29" t="str">
         <f aca="false">IF($M377="","",$M377*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O377" s="29" t="str">
-        <f aca="false">IF($M377="","",$M377*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P377" s="28"/>
@@ -22125,12 +21125,9 @@
       </c>
       <c r="L378" s="28"/>
       <c r="M378" s="27"/>
-      <c r="N378" s="29" t="str">
+      <c r="N378" s="28"/>
+      <c r="O378" s="29" t="str">
         <f aca="false">IF($M378="","",$M378*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O378" s="29" t="str">
-        <f aca="false">IF($M378="","",$M378*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P378" s="28"/>
@@ -22179,12 +21176,9 @@
       </c>
       <c r="L379" s="28"/>
       <c r="M379" s="27"/>
-      <c r="N379" s="29" t="str">
+      <c r="N379" s="28"/>
+      <c r="O379" s="29" t="str">
         <f aca="false">IF($M379="","",$M379*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O379" s="29" t="str">
-        <f aca="false">IF($M379="","",$M379*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P379" s="28"/>
@@ -22233,12 +21227,9 @@
       </c>
       <c r="L380" s="28"/>
       <c r="M380" s="27"/>
-      <c r="N380" s="29" t="str">
+      <c r="N380" s="28"/>
+      <c r="O380" s="29" t="str">
         <f aca="false">IF($M380="","",$M380*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O380" s="29" t="str">
-        <f aca="false">IF($M380="","",$M380*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P380" s="28"/>
@@ -22287,12 +21278,9 @@
       </c>
       <c r="L381" s="28"/>
       <c r="M381" s="27"/>
-      <c r="N381" s="29" t="str">
+      <c r="N381" s="28"/>
+      <c r="O381" s="29" t="str">
         <f aca="false">IF($M381="","",$M381*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O381" s="29" t="str">
-        <f aca="false">IF($M381="","",$M381*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P381" s="28"/>
@@ -22341,12 +21329,9 @@
       </c>
       <c r="L382" s="28"/>
       <c r="M382" s="27"/>
-      <c r="N382" s="29" t="str">
+      <c r="N382" s="28"/>
+      <c r="O382" s="29" t="str">
         <f aca="false">IF($M382="","",$M382*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O382" s="29" t="str">
-        <f aca="false">IF($M382="","",$M382*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P382" s="28"/>
@@ -22395,12 +21380,9 @@
       </c>
       <c r="L383" s="28"/>
       <c r="M383" s="27"/>
-      <c r="N383" s="29" t="str">
+      <c r="N383" s="28"/>
+      <c r="O383" s="29" t="str">
         <f aca="false">IF($M383="","",$M383*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O383" s="29" t="str">
-        <f aca="false">IF($M383="","",$M383*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P383" s="28"/>
@@ -22449,12 +21431,9 @@
       </c>
       <c r="L384" s="28"/>
       <c r="M384" s="27"/>
-      <c r="N384" s="29" t="str">
+      <c r="N384" s="28"/>
+      <c r="O384" s="29" t="str">
         <f aca="false">IF($M384="","",$M384*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O384" s="29" t="str">
-        <f aca="false">IF($M384="","",$M384*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P384" s="28"/>
@@ -22503,12 +21482,9 @@
       </c>
       <c r="L385" s="28"/>
       <c r="M385" s="27"/>
-      <c r="N385" s="29" t="str">
+      <c r="N385" s="28"/>
+      <c r="O385" s="29" t="str">
         <f aca="false">IF($M385="","",$M385*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O385" s="29" t="str">
-        <f aca="false">IF($M385="","",$M385*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P385" s="28"/>
@@ -22557,12 +21533,9 @@
       </c>
       <c r="L386" s="28"/>
       <c r="M386" s="27"/>
-      <c r="N386" s="29" t="str">
+      <c r="N386" s="28"/>
+      <c r="O386" s="29" t="str">
         <f aca="false">IF($M386="","",$M386*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O386" s="29" t="str">
-        <f aca="false">IF($M386="","",$M386*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P386" s="28"/>
@@ -22611,12 +21584,9 @@
       </c>
       <c r="L387" s="28"/>
       <c r="M387" s="27"/>
-      <c r="N387" s="29" t="str">
+      <c r="N387" s="28"/>
+      <c r="O387" s="29" t="str">
         <f aca="false">IF($M387="","",$M387*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O387" s="29" t="str">
-        <f aca="false">IF($M387="","",$M387*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P387" s="28"/>
@@ -22665,12 +21635,9 @@
       </c>
       <c r="L388" s="28"/>
       <c r="M388" s="27"/>
-      <c r="N388" s="29" t="str">
+      <c r="N388" s="28"/>
+      <c r="O388" s="29" t="str">
         <f aca="false">IF($M388="","",$M388*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O388" s="29" t="str">
-        <f aca="false">IF($M388="","",$M388*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P388" s="28"/>
@@ -22719,12 +21686,9 @@
       </c>
       <c r="L389" s="28"/>
       <c r="M389" s="27"/>
-      <c r="N389" s="29" t="str">
+      <c r="N389" s="28"/>
+      <c r="O389" s="29" t="str">
         <f aca="false">IF($M389="","",$M389*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O389" s="29" t="str">
-        <f aca="false">IF($M389="","",$M389*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P389" s="28"/>
@@ -22773,12 +21737,9 @@
       </c>
       <c r="L390" s="28"/>
       <c r="M390" s="27"/>
-      <c r="N390" s="29" t="str">
+      <c r="N390" s="28"/>
+      <c r="O390" s="29" t="str">
         <f aca="false">IF($M390="","",$M390*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O390" s="29" t="str">
-        <f aca="false">IF($M390="","",$M390*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P390" s="28"/>
@@ -22827,12 +21788,9 @@
       </c>
       <c r="L391" s="28"/>
       <c r="M391" s="27"/>
-      <c r="N391" s="29" t="str">
+      <c r="N391" s="28"/>
+      <c r="O391" s="29" t="str">
         <f aca="false">IF($M391="","",$M391*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O391" s="29" t="str">
-        <f aca="false">IF($M391="","",$M391*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P391" s="28"/>
@@ -22881,12 +21839,9 @@
       </c>
       <c r="L392" s="28"/>
       <c r="M392" s="27"/>
-      <c r="N392" s="29" t="str">
+      <c r="N392" s="28"/>
+      <c r="O392" s="29" t="str">
         <f aca="false">IF($M392="","",$M392*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O392" s="29" t="str">
-        <f aca="false">IF($M392="","",$M392*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P392" s="28"/>
@@ -22935,12 +21890,9 @@
       </c>
       <c r="L393" s="28"/>
       <c r="M393" s="27"/>
-      <c r="N393" s="29" t="str">
+      <c r="N393" s="28"/>
+      <c r="O393" s="29" t="str">
         <f aca="false">IF($M393="","",$M393*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O393" s="29" t="str">
-        <f aca="false">IF($M393="","",$M393*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P393" s="28"/>
@@ -22989,12 +21941,9 @@
       </c>
       <c r="L394" s="28"/>
       <c r="M394" s="27"/>
-      <c r="N394" s="29" t="str">
+      <c r="N394" s="28"/>
+      <c r="O394" s="29" t="str">
         <f aca="false">IF($M394="","",$M394*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O394" s="29" t="str">
-        <f aca="false">IF($M394="","",$M394*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P394" s="28"/>
@@ -23043,12 +21992,9 @@
       </c>
       <c r="L395" s="28"/>
       <c r="M395" s="27"/>
-      <c r="N395" s="29" t="str">
+      <c r="N395" s="28"/>
+      <c r="O395" s="29" t="str">
         <f aca="false">IF($M395="","",$M395*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O395" s="29" t="str">
-        <f aca="false">IF($M395="","",$M395*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P395" s="28"/>
@@ -23097,12 +22043,9 @@
       </c>
       <c r="L396" s="28"/>
       <c r="M396" s="27"/>
-      <c r="N396" s="29" t="str">
+      <c r="N396" s="28"/>
+      <c r="O396" s="29" t="str">
         <f aca="false">IF($M396="","",$M396*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O396" s="29" t="str">
-        <f aca="false">IF($M396="","",$M396*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P396" s="28"/>
@@ -23151,12 +22094,9 @@
       </c>
       <c r="L397" s="28"/>
       <c r="M397" s="27"/>
-      <c r="N397" s="29" t="str">
+      <c r="N397" s="28"/>
+      <c r="O397" s="29" t="str">
         <f aca="false">IF($M397="","",$M397*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O397" s="29" t="str">
-        <f aca="false">IF($M397="","",$M397*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P397" s="28"/>
@@ -23205,12 +22145,9 @@
       </c>
       <c r="L398" s="28"/>
       <c r="M398" s="27"/>
-      <c r="N398" s="29" t="str">
+      <c r="N398" s="28"/>
+      <c r="O398" s="29" t="str">
         <f aca="false">IF($M398="","",$M398*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O398" s="29" t="str">
-        <f aca="false">IF($M398="","",$M398*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P398" s="28"/>
@@ -23259,12 +22196,9 @@
       </c>
       <c r="L399" s="28"/>
       <c r="M399" s="27"/>
-      <c r="N399" s="29" t="str">
+      <c r="N399" s="28"/>
+      <c r="O399" s="29" t="str">
         <f aca="false">IF($M399="","",$M399*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O399" s="29" t="str">
-        <f aca="false">IF($M399="","",$M399*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P399" s="28"/>
@@ -23313,12 +22247,9 @@
       </c>
       <c r="L400" s="28"/>
       <c r="M400" s="27"/>
-      <c r="N400" s="29" t="str">
+      <c r="N400" s="28"/>
+      <c r="O400" s="29" t="str">
         <f aca="false">IF($M400="","",$M400*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O400" s="29" t="str">
-        <f aca="false">IF($M400="","",$M400*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P400" s="28"/>
@@ -23367,12 +22298,9 @@
       </c>
       <c r="L401" s="28"/>
       <c r="M401" s="27"/>
-      <c r="N401" s="29" t="str">
+      <c r="N401" s="28"/>
+      <c r="O401" s="29" t="str">
         <f aca="false">IF($M401="","",$M401*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O401" s="29" t="str">
-        <f aca="false">IF($M401="","",$M401*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P401" s="28"/>
@@ -23421,12 +22349,9 @@
       </c>
       <c r="L402" s="28"/>
       <c r="M402" s="27"/>
-      <c r="N402" s="29" t="str">
+      <c r="N402" s="28"/>
+      <c r="O402" s="29" t="str">
         <f aca="false">IF($M402="","",$M402*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O402" s="29" t="str">
-        <f aca="false">IF($M402="","",$M402*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P402" s="28"/>
@@ -23475,12 +22400,9 @@
       </c>
       <c r="L403" s="28"/>
       <c r="M403" s="27"/>
-      <c r="N403" s="29" t="str">
+      <c r="N403" s="28"/>
+      <c r="O403" s="29" t="str">
         <f aca="false">IF($M403="","",$M403*Config!$B$6)</f>
-        <v/>
-      </c>
-      <c r="O403" s="29" t="str">
-        <f aca="false">IF($M403="","",$M403*Config!$B$7)</f>
         <v/>
       </c>
       <c r="P403" s="28"/>
@@ -23562,44 +22484,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B5" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A5)</f>
@@ -23636,7 +22558,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B6" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A6)</f>
@@ -23673,7 +22595,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B7" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A7)</f>
@@ -23710,7 +22632,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B8" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A8)</f>
@@ -23747,7 +22669,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A9)</f>
@@ -23784,7 +22706,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B10" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A10)</f>
@@ -23821,7 +22743,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A11)</f>
@@ -23837,15 +22759,15 @@
       </c>
       <c r="E11" s="36" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$R$3:$R$403,'Registo Diário'!$D$3:$D$403,$A11)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F11" s="37" t="n">
         <f aca="false">IF($C11=0,"",$E11/$C11)</f>
-        <v>16.44</v>
+        <v>17.2523076923077</v>
       </c>
       <c r="G11" s="36" t="n">
         <f aca="false">IF($I11=0,"",$E11/$I11)</f>
-        <v>0.875901639344263</v>
+        <v>0.919180327868853</v>
       </c>
       <c r="H11" s="35" t="n">
         <f aca="false">IF($C11=0,"",SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$D$3:$D$403,$A11)/$C11)</f>
@@ -23858,7 +22780,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$D$3:$D$403,$A12)</f>
@@ -23895,7 +22817,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="38" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B13" s="39" t="n">
         <f aca="false">SUM(B5:B12)</f>
@@ -23911,15 +22833,15 @@
       </c>
       <c r="E13" s="41" t="n">
         <f aca="false">SUM(E5:E12)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F13" s="41" t="n">
         <f aca="false">IF($C13=0,"",$E13/$C13)</f>
-        <v>16.44</v>
+        <v>17.2523076923077</v>
       </c>
       <c r="G13" s="41" t="n">
         <f aca="false">IF($I13=0,"",$E13/$I13)</f>
-        <v>0.875901639344263</v>
+        <v>0.919180327868853</v>
       </c>
       <c r="H13" s="40" t="n">
         <f aca="false">IF($C13=0,"",SUMPRODUCT($H5:$H12,$C5:$C12)/$C13)</f>
@@ -23973,44 +22895,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B5" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A5)</f>
@@ -24047,7 +22969,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B6" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A6)</f>
@@ -24084,7 +23006,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B7" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A7)</f>
@@ -24121,7 +23043,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B8" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A8)</f>
@@ -24137,15 +23059,15 @@
       </c>
       <c r="E8" s="36" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$R$3:$R$403,'Registo Diário'!$E$3:$E$403,$A8)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F8" s="37" t="n">
         <f aca="false">IF($C8=0,"",$E8/$C8)</f>
-        <v>16.44</v>
+        <v>17.2523076923077</v>
       </c>
       <c r="G8" s="36" t="n">
         <f aca="false">IF($I8=0,"",$E8/$I8)</f>
-        <v>0.875901639344263</v>
+        <v>0.919180327868853</v>
       </c>
       <c r="H8" s="35" t="n">
         <f aca="false">IF($C8=0,"",SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$E$3:$E$403,$A8)/$C8)</f>
@@ -24158,7 +23080,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A9)</f>
@@ -24195,7 +23117,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B10" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A10)</f>
@@ -24232,7 +23154,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A11)</f>
@@ -24269,7 +23191,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A12)</f>
@@ -24306,7 +23228,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B13" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A13)</f>
@@ -24343,7 +23265,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B14" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A14)</f>
@@ -24380,7 +23302,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B15" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A15)</f>
@@ -24417,7 +23339,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B16" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A16)</f>
@@ -24454,7 +23376,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B17" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A17)</f>
@@ -24491,7 +23413,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B18" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A18)</f>
@@ -24528,7 +23450,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A19)</f>
@@ -24565,7 +23487,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$E$3:$E$403,$A20)</f>
@@ -24602,7 +23524,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B21" s="39" t="n">
         <f aca="false">SUM(B5:B20)</f>
@@ -24618,15 +23540,15 @@
       </c>
       <c r="E21" s="41" t="n">
         <f aca="false">SUM(E5:E20)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F21" s="41" t="n">
         <f aca="false">IF($C21=0,"",$E21/$C21)</f>
-        <v>16.44</v>
+        <v>17.2523076923077</v>
       </c>
       <c r="G21" s="41" t="n">
         <f aca="false">IF($I21=0,"",$E21/$I21)</f>
-        <v>0.875901639344263</v>
+        <v>0.919180327868853</v>
       </c>
       <c r="H21" s="40" t="n">
         <f aca="false">IF($C21=0,"",SUMPRODUCT($H5:$H20,$C5:$C20)/$C21)</f>
@@ -24680,44 +23602,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B5" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$B$3:$B$403,$A5)</f>
@@ -24754,7 +23676,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B6" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$B$3:$B$403,$A6)</f>
@@ -24791,7 +23713,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B7" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$B$3:$B$403,$A7)</f>
@@ -24828,7 +23750,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B8" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$B$3:$B$403,$A8)</f>
@@ -24865,7 +23787,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$B$3:$B$403,$A9)</f>
@@ -24902,7 +23824,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B10" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$B$3:$B$403,$A10)</f>
@@ -24918,15 +23840,15 @@
       </c>
       <c r="E10" s="36" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$R$3:$R$403,'Registo Diário'!$B$3:$B$403,$A10)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F10" s="37" t="n">
         <f aca="false">IF($C10=0,"",$E10/$C10)</f>
-        <v>16.44</v>
+        <v>17.2523076923077</v>
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">IF($I10=0,"",$E10/$I10)</f>
-        <v>0.875901639344263</v>
+        <v>0.919180327868853</v>
       </c>
       <c r="H10" s="35" t="n">
         <f aca="false">IF($C10=0,"",SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$B$3:$B$403,$A10)/$C10)</f>
@@ -24939,7 +23861,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">COUNTIFS('Registo Diário'!$B$3:$B$403,$A11)</f>
@@ -24976,7 +23898,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B12" s="39" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -24992,15 +23914,15 @@
       </c>
       <c r="E12" s="41" t="n">
         <f aca="false">SUM(E5:E11)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F12" s="41" t="n">
         <f aca="false">IF($C12=0,"",$E12/$C12)</f>
-        <v>16.44</v>
+        <v>17.2523076923077</v>
       </c>
       <c r="G12" s="41" t="n">
         <f aca="false">IF($I12=0,"",$E12/$I12)</f>
-        <v>0.875901639344263</v>
+        <v>0.919180327868853</v>
       </c>
       <c r="H12" s="40" t="n">
         <f aca="false">IF($C12=0,"",SUMPRODUCT($H5:$H11,$C5:$C11)/$C12)</f>
@@ -25039,26 +23961,29 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="42" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -25069,42 +23994,50 @@
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+    </row>
+    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>124</v>
+        <v>133</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="43" t="n">
-        <f aca="false">EOMONTH(Config!$B$19,0)</f>
+        <f aca="false">EOMONTH(Config!$B$18,0)</f>
         <v>46295</v>
       </c>
       <c r="B5" s="34" t="n">
@@ -25121,19 +24054,19 @@
       </c>
       <c r="E5" s="36" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$R$3:$R$403,'Registo Diário'!$C$3:$C$403,$A5)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F5" s="44" t="n">
-        <f aca="false">IF($B5=0,0,Config!$B$17)</f>
-        <v>210</v>
+        <f aca="false">IF($B5=0,0,Config!$B$16)</f>
+        <v>390</v>
       </c>
       <c r="G5" s="37" t="n">
         <f aca="false">$E5-$F5</f>
-        <v>-103.14</v>
+        <v>-277.86</v>
       </c>
       <c r="H5" s="37" t="n">
         <f aca="false">IF($C5=0,"",$G5/$C5)</f>
-        <v>-15.8676923076923</v>
+        <v>-42.7476923076923</v>
       </c>
       <c r="I5" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$M$3:$M$403,'Registo Diário'!$C$3:$C$403,$A5)</f>
@@ -25142,6 +24075,14 @@
       <c r="J5" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A5)</f>
         <v>14</v>
+      </c>
+      <c r="K5" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A5)</f>
+        <v>11.8</v>
+      </c>
+      <c r="L5" s="36" t="n">
+        <f aca="false">IF($I5=0,"",$K5/$I5*100)</f>
+        <v>9.67213114754098</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25166,7 +24107,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="44" t="n">
-        <f aca="false">IF($B6=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B6=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G6" s="37" t="n">
@@ -25184,6 +24125,14 @@
       <c r="J6" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A6)</f>
         <v>0</v>
+      </c>
+      <c r="K6" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="36" t="str">
+        <f aca="false">IF($I6=0,"",$K6/$I6*100)</f>
+        <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25208,7 +24157,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="44" t="n">
-        <f aca="false">IF($B7=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B7=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G7" s="37" t="n">
@@ -25226,6 +24175,14 @@
       <c r="J7" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A7)</f>
         <v>0</v>
+      </c>
+      <c r="K7" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="36" t="str">
+        <f aca="false">IF($I7=0,"",$K7/$I7*100)</f>
+        <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25250,7 +24207,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="44" t="n">
-        <f aca="false">IF($B8=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B8=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G8" s="37" t="n">
@@ -25268,6 +24225,14 @@
       <c r="J8" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A8)</f>
         <v>0</v>
+      </c>
+      <c r="K8" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="36" t="str">
+        <f aca="false">IF($I8=0,"",$K8/$I8*100)</f>
+        <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25292,7 +24257,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="44" t="n">
-        <f aca="false">IF($B9=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B9=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G9" s="37" t="n">
@@ -25310,6 +24275,14 @@
       <c r="J9" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A9)</f>
         <v>0</v>
+      </c>
+      <c r="K9" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="36" t="str">
+        <f aca="false">IF($I9=0,"",$K9/$I9*100)</f>
+        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25334,7 +24307,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="44" t="n">
-        <f aca="false">IF($B10=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B10=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G10" s="37" t="n">
@@ -25352,6 +24325,14 @@
       <c r="J10" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A10)</f>
         <v>0</v>
+      </c>
+      <c r="K10" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="36" t="str">
+        <f aca="false">IF($I10=0,"",$K10/$I10*100)</f>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25376,7 +24357,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="44" t="n">
-        <f aca="false">IF($B11=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B11=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G11" s="37" t="n">
@@ -25394,6 +24375,14 @@
       <c r="J11" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A11)</f>
         <v>0</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="36" t="str">
+        <f aca="false">IF($I11=0,"",$K11/$I11*100)</f>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25418,7 +24407,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="44" t="n">
-        <f aca="false">IF($B12=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B12=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G12" s="37" t="n">
@@ -25436,6 +24425,14 @@
       <c r="J12" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A12)</f>
         <v>0</v>
+      </c>
+      <c r="K12" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="36" t="str">
+        <f aca="false">IF($I12=0,"",$K12/$I12*100)</f>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25460,7 +24457,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="44" t="n">
-        <f aca="false">IF($B13=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B13=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G13" s="37" t="n">
@@ -25478,6 +24475,14 @@
       <c r="J13" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A13)</f>
         <v>0</v>
+      </c>
+      <c r="K13" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="36" t="str">
+        <f aca="false">IF($I13=0,"",$K13/$I13*100)</f>
+        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25502,7 +24507,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="44" t="n">
-        <f aca="false">IF($B14=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B14=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G14" s="37" t="n">
@@ -25520,6 +24525,14 @@
       <c r="J14" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A14)</f>
         <v>0</v>
+      </c>
+      <c r="K14" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A14)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="36" t="str">
+        <f aca="false">IF($I14=0,"",$K14/$I14*100)</f>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25544,7 +24557,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="44" t="n">
-        <f aca="false">IF($B15=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B15=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G15" s="37" t="n">
@@ -25562,6 +24575,14 @@
       <c r="J15" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A15)</f>
         <v>0</v>
+      </c>
+      <c r="K15" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A15)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="36" t="str">
+        <f aca="false">IF($I15=0,"",$K15/$I15*100)</f>
+        <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25586,7 +24607,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="44" t="n">
-        <f aca="false">IF($B16=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B16=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G16" s="37" t="n">
@@ -25604,6 +24625,14 @@
       <c r="J16" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A16)</f>
         <v>0</v>
+      </c>
+      <c r="K16" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A16)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="36" t="str">
+        <f aca="false">IF($I16=0,"",$K16/$I16*100)</f>
+        <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25628,7 +24657,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="44" t="n">
-        <f aca="false">IF($B17=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B17=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G17" s="37" t="n">
@@ -25646,6 +24675,14 @@
       <c r="J17" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A17)</f>
         <v>0</v>
+      </c>
+      <c r="K17" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A17)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="36" t="str">
+        <f aca="false">IF($I17=0,"",$K17/$I17*100)</f>
+        <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25670,7 +24707,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="44" t="n">
-        <f aca="false">IF($B18=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B18=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G18" s="37" t="n">
@@ -25688,6 +24725,14 @@
       <c r="J18" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A18)</f>
         <v>0</v>
+      </c>
+      <c r="K18" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A18)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="36" t="str">
+        <f aca="false">IF($I18=0,"",$K18/$I18*100)</f>
+        <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25712,7 +24757,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="44" t="n">
-        <f aca="false">IF($B19=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B19=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G19" s="37" t="n">
@@ -25730,6 +24775,14 @@
       <c r="J19" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A19)</f>
         <v>0</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A19)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="36" t="str">
+        <f aca="false">IF($I19=0,"",$K19/$I19*100)</f>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25754,7 +24807,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="44" t="n">
-        <f aca="false">IF($B20=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B20=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G20" s="37" t="n">
@@ -25772,6 +24825,14 @@
       <c r="J20" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A20)</f>
         <v>0</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A20)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="36" t="str">
+        <f aca="false">IF($I20=0,"",$K20/$I20*100)</f>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25796,7 +24857,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="44" t="n">
-        <f aca="false">IF($B21=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B21=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G21" s="37" t="n">
@@ -25814,6 +24875,14 @@
       <c r="J21" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A21)</f>
         <v>0</v>
+      </c>
+      <c r="K21" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A21)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="36" t="str">
+        <f aca="false">IF($I21=0,"",$K21/$I21*100)</f>
+        <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25838,7 +24907,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="44" t="n">
-        <f aca="false">IF($B22=0,0,Config!$B$17)</f>
+        <f aca="false">IF($B22=0,0,Config!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G22" s="37" t="n">
@@ -25857,10 +24926,18 @@
         <f aca="false">SUMIFS('Registo Diário'!$I$3:$I$403,'Registo Diário'!$C$3:$C$403,$A22)</f>
         <v>0</v>
       </c>
+      <c r="K22" s="36" t="n">
+        <f aca="false">SUMIFS('Registo Diário'!$N$3:$N$403,'Registo Diário'!$C$3:$C$403,$A22)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="36" t="str">
+        <f aca="false">IF($I22=0,"",$K22/$I22*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B23" s="39" t="n">
         <f aca="false">SUM(B5:B22)</f>
@@ -25876,19 +24953,19 @@
       </c>
       <c r="E23" s="41" t="n">
         <f aca="false">SUM(E5:E22)</f>
-        <v>106.86</v>
+        <v>112.14</v>
       </c>
       <c r="F23" s="41" t="n">
         <f aca="false">SUM(F5:F22)</f>
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="G23" s="41" t="n">
         <f aca="false">SUM(G5:G22)</f>
-        <v>-103.14</v>
+        <v>-277.86</v>
       </c>
       <c r="H23" s="41" t="n">
         <f aca="false">IF($C23=0,"",$G23/$C23)</f>
-        <v>-15.8676923076923</v>
+        <v>-42.7476923076923</v>
       </c>
       <c r="I23" s="39" t="n">
         <f aca="false">SUM(I5:I22)</f>
@@ -25898,13 +24975,21 @@
         <f aca="false">SUM(J5:J22)</f>
         <v>14</v>
       </c>
+      <c r="K23" s="41" t="n">
+        <f aca="false">SUM(K5:K22)</f>
+        <v>11.8</v>
+      </c>
+      <c r="L23" s="41" t="n">
+        <f aca="false">IF($I23=0,"",$K23/$I23*100)</f>
+        <v>9.67213114754098</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
@@ -25914,11 +24999,13 @@
       <c r="H25" s="46"/>
       <c r="I25" s="46"/>
       <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B25:L25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -25935,12 +25022,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
@@ -25948,308 +25035,284 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D1" s="47" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E1" s="47" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F1" s="47" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D2" s="48" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F2" s="48" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D3" s="48" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="49" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
       <c r="D4" s="48" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B5" s="50" t="n">
         <v>0.25</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F5" s="48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="52" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="49"/>
+      <c r="C11" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="52" t="n">
+        <v>390</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="52"/>
+      <c r="C13" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="48" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="52" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="48" t="s">
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="48" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" s="52" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="F7" s="48" t="s">
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="41" t="n">
+        <f aca="false">SUM(B12:B15)</f>
+        <v>390</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="E16" s="48" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="48" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="48" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="52" t="n">
-        <v>90</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="B11" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="52" t="n">
-        <v>60</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="52" t="n">
-        <v>25</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="B17" s="41" t="n">
-        <f aca="false">SUM(B10:B16)</f>
-        <v>210</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>108</v>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="56" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="B19" s="54" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>156</v>
-      </c>
       <c r="D19" s="46" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E19" s="46"/>
       <c r="F19" s="46"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
       <c r="D20" s="46"/>
       <c r="E20" s="46"/>
       <c r="F20" s="46"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
+      <c r="A21" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>167</v>
+      </c>
       <c r="D21" s="46"/>
       <c r="E21" s="46"/>
       <c r="F21" s="46"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="C22" s="56" t="s">
-        <v>160</v>
+      <c r="A22" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="57" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="56" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C24" s="56" t="s">
-        <v>164</v>
+      <c r="A23" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="58" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -26263,5 +25326,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Controlo_TVDE_Lisboa.xlsx
+++ b/Controlo_TVDE_Lisboa.xlsx
@@ -134,30 +134,8 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="B13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Valor por preencher. Enquanto estiver vazio conta como 0 € e o resultado mensal aparece melhor do que é na realidade.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="177">
   <si>
     <t xml:space="preserve">Controlo TVDE — Lisboa</t>
   </si>
@@ -621,28 +599,43 @@
     <t xml:space="preserve">Prestação mensal do Tesla.</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguro</t>
+    <t xml:space="preserve">Seguro (970 €/ano ÷ 12)</t>
   </si>
   <si>
-    <t xml:space="preserve">A PREENCHER — seguro com cobertura de atividade TVDE. Mete o valor mensal assim que o tiveres.</t>
+    <t xml:space="preserve">Calculado a partir do valor anual do seguro, na secção «Custos anuais» abaixo. Muda lá o valor e este acompanha.</t>
   </si>
   <si>
     <t xml:space="preserve">Outros custos fixos 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Livre. Ex.: contabilidade, licenças TVDE mensalizadas, telemóvel, IUC e inspeção divididos por 12.</t>
+    <t xml:space="preserve">Livre, para um custo que pagues TODOS OS MESES. Ex.: contabilidade, telemóvel.</t>
   </si>
   <si>
-    <t xml:space="preserve">Outros custos fixos 2</t>
+    <t xml:space="preserve">Outros custos anuais ÷ 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Livre.</t>
+    <t xml:space="preserve">Calculado a partir do valor anual da secção abaixo. Ex.: IUC, inspeção, licenças TVDE.</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL de custos fixos mensais</t>
   </si>
   <si>
     <t xml:space="preserve">Só entram aqui os custos que listares acima. O que pagares e não estiver nesta lista não é abatido em lado nenhum — o resultado mensal sai por isso melhor do que a realidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custos anuais (entram mensalizados na tabela acima)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro (anual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro com cobertura de atividade TVDE. 970 €/ano = 80,83 €/mês, já refletido na tabela acima.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outros custos anuais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soma aqui o que pagas uma vez por ano: IUC, inspeção, certificado de motorista TVDE, dístico do veículo.</t>
   </si>
   <si>
     <t xml:space="preserve">Primeiro mês de atividade</t>
@@ -24037,7 +24030,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="43" t="n">
-        <f aca="false">EOMONTH(Config!$B$18,0)</f>
+        <f aca="false">EOMONTH(Config!$B$22,0)</f>
         <v>46295</v>
       </c>
       <c r="B5" s="34" t="n">
@@ -24058,15 +24051,15 @@
       </c>
       <c r="F5" s="44" t="n">
         <f aca="false">IF($B5=0,0,Config!$B$16)</f>
-        <v>390</v>
+        <v>470.833333333333</v>
       </c>
       <c r="G5" s="37" t="n">
         <f aca="false">$E5-$F5</f>
-        <v>-277.86</v>
+        <v>-358.693333333333</v>
       </c>
       <c r="H5" s="37" t="n">
         <f aca="false">IF($C5=0,"",$G5/$C5)</f>
-        <v>-42.7476923076923</v>
+        <v>-55.1835897435897</v>
       </c>
       <c r="I5" s="34" t="n">
         <f aca="false">SUMIFS('Registo Diário'!$M$3:$M$403,'Registo Diário'!$C$3:$C$403,$A5)</f>
@@ -24957,15 +24950,15 @@
       </c>
       <c r="F23" s="41" t="n">
         <f aca="false">SUM(F5:F22)</f>
-        <v>390</v>
+        <v>470.833333333333</v>
       </c>
       <c r="G23" s="41" t="n">
         <f aca="false">SUM(G5:G22)</f>
-        <v>-277.86</v>
+        <v>-358.693333333333</v>
       </c>
       <c r="H23" s="41" t="n">
         <f aca="false">IF($C23=0,"",$G23/$C23)</f>
-        <v>-42.7476923076923</v>
+        <v>-55.1835897435897</v>
       </c>
       <c r="I23" s="39" t="n">
         <f aca="false">SUM(I5:I22)</f>
@@ -25022,7 +25015,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -25204,7 +25197,10 @@
       <c r="A13" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="B13" s="52"/>
+      <c r="B13" s="30" t="n">
+        <f aca="false">B19/12</f>
+        <v>80.8333333333333</v>
+      </c>
       <c r="C13" s="51" t="s">
         <v>155</v>
       </c>
@@ -25230,7 +25226,8 @@
       <c r="A15" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="30" t="n">
+        <f aca="false">B20/12</f>
         <v>0</v>
       </c>
       <c r="C15" s="51" t="s">
@@ -25246,7 +25243,7 @@
       </c>
       <c r="B16" s="41" t="n">
         <f aca="false">SUM(B12:B15)</f>
-        <v>390</v>
+        <v>470.833333333333</v>
       </c>
       <c r="C16" s="55" t="s">
         <v>161</v>
@@ -25261,63 +25258,92 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="56" t="n">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="52" t="n">
+        <v>970</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="56" t="n">
         <v>46266</v>
       </c>
-      <c r="C18" s="51" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D19" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="C21" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="59" t="s">
+      <c r="C22" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="D22" s="46" t="s">
         <v>169</v>
       </c>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="60" t="s">
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="57" t="s">
         <v>171</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="59" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D19:F21"/>
+    <mergeCell ref="D22:F24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -25326,6 +25352,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>